--- a/20240725DZ90A1X compressor curve - 20240725.xlsx
+++ b/20240725DZ90A1X compressor curve - 20240725.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20364"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30305"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aabdel203\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\refrigerator-volume-calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB619789-8358-4A7F-B285-CDF4F4041277}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE96931-D465-46A7-9ABF-69E38CA6D039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19275" yWindow="-3910" windowWidth="9750" windowHeight="11355" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="变更记录" sheetId="1" state="hidden" r:id="rId1"/>
@@ -793,7 +793,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -803,6 +803,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -917,7 +923,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -942,7 +948,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -963,129 +969,101 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1094,26 +1072,29 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1124,42 +1105,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1169,31 +1114,64 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1202,8 +1180,23 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1296,7 +1289,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1811,7 +1804,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1967,7 +1960,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-US" altLang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2172,7 +2165,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2687,7 +2680,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2843,7 +2836,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-US" altLang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3049,7 +3042,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3579,7 +3572,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3739,7 +3732,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-US" altLang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -4480,7 +4473,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -4828,7 +4821,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5343,7 +5336,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5704,7 +5697,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6219,7 +6212,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -6583,7 +6576,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7098,7 +7091,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -7248,7 +7241,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -7454,7 +7447,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7969,7 +7962,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -8119,7 +8112,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -8325,7 +8318,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -8840,7 +8833,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -9197,7 +9190,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -9712,7 +9705,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -9868,7 +9861,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-US" altLang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -10074,7 +10067,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -10604,7 +10597,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -10764,7 +10757,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-US" altLang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -11505,7 +11498,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="zh-CN"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -19188,15 +19181,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.5" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -19455,222 +19448,222 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="23.4">
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
     </row>
     <row r="2" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="28"/>
     </row>
     <row r="3" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="88" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="89"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="30"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="88" t="s">
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="89"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="30"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="88" t="s">
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="89"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="30"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="88" t="s">
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="89"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="30"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="88" t="s">
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="89"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="31"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="30"/>
     </row>
     <row r="8" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="88" t="s">
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="89"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="30"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="88" t="s">
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="89"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="30"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="32"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
     </row>
     <row r="12" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="23"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="22"/>
     </row>
     <row r="13" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="23"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="67"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="65" t="s">
+      <c r="G14" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="24"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" spans="2:11" ht="17.399999999999999" customHeight="1">
-      <c r="B15" s="78"/>
-      <c r="C15" s="80" t="s">
+      <c r="B15" s="56"/>
+      <c r="C15" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="46" t="s">
+      <c r="D15" s="61"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="80" t="s">
+      <c r="G15" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="81"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="24"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="2:11" ht="17.399999999999999" customHeight="1">
       <c r="B16" s="11" t="s">
@@ -19682,28 +19675,28 @@
       <c r="D16" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="24"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B17" s="21">
+      <c r="B17" s="17">
         <v>-35</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="41">
         <v>126.60247455270041</v>
       </c>
       <c r="D17" s="9">
@@ -19714,7 +19707,7 @@
         <f>C17*0.86</f>
         <v>108.87812811532235</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="42">
         <v>90.279153313447765</v>
       </c>
       <c r="G17" s="13">
@@ -19729,14 +19722,14 @@
         <f>E17/F17</f>
         <v>1.2060162741812526</v>
       </c>
-      <c r="J17" s="25"/>
-      <c r="L17" s="26"/>
+      <c r="J17" s="24"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B18" s="21">
+      <c r="B18" s="17">
         <v>-30</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="41">
         <v>159.19075480873741</v>
       </c>
       <c r="D18" s="9">
@@ -19747,7 +19740,7 @@
         <f t="shared" ref="E18:E22" si="1">C18*0.86</f>
         <v>136.90404913551416</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="42">
         <v>105.47662725419623</v>
       </c>
       <c r="G18" s="13">
@@ -19762,14 +19755,14 @@
         <f t="shared" ref="I18:I22" si="4">E18/F18</f>
         <v>1.2979562648090612</v>
       </c>
-      <c r="J18" s="25"/>
-      <c r="L18" s="26"/>
+      <c r="J18" s="24"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B19" s="21">
+      <c r="B19" s="17">
         <v>-25</v>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="41">
         <v>199.00329420878455</v>
       </c>
       <c r="D19" s="9">
@@ -19780,7 +19773,7 @@
         <f t="shared" si="1"/>
         <v>171.1428330195547</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="42">
         <v>121.10874367936796</v>
       </c>
       <c r="G19" s="13">
@@ -19795,14 +19788,14 @@
         <f t="shared" si="4"/>
         <v>1.4131335840841566</v>
       </c>
-      <c r="J19" s="25"/>
-      <c r="L19" s="26"/>
+      <c r="J19" s="24"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B20" s="21">
+      <c r="B20" s="17">
         <v>-20</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="41">
         <v>247.22899976895181</v>
       </c>
       <c r="D20" s="9">
@@ -19813,7 +19806,7 @@
         <f t="shared" si="1"/>
         <v>212.61693980129854</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="42">
         <v>136.7463842013276</v>
       </c>
       <c r="G20" s="13">
@@ -19828,14 +19821,14 @@
         <f t="shared" si="4"/>
         <v>1.5548267769059911</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="27"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="26"/>
     </row>
     <row r="21" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B21" s="21">
+      <c r="B21" s="17">
         <v>-15</v>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="41">
         <v>305.0567785053496</v>
       </c>
       <c r="D21" s="9">
@@ -19846,7 +19839,7 @@
         <f t="shared" si="1"/>
         <v>262.34882951460065</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="42">
         <v>151.96043043243981</v>
       </c>
       <c r="G21" s="13">
@@ -19861,14 +19854,14 @@
         <f t="shared" si="4"/>
         <v>1.7264285759656262</v>
       </c>
-      <c r="J21" s="25"/>
-      <c r="K21" s="27"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="26"/>
     </row>
     <row r="22" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B22" s="21">
+      <c r="B22" s="17">
         <v>-10</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="41">
         <v>373.67553743408791</v>
       </c>
       <c r="D22" s="9">
@@ -19879,7 +19872,7 @@
         <f t="shared" si="1"/>
         <v>321.36096219331563</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="42">
         <v>166.32176398506914</v>
       </c>
       <c r="G22" s="13">
@@ -19894,73 +19887,73 @@
         <f t="shared" si="4"/>
         <v>1.9321642248946116</v>
       </c>
-      <c r="J22" s="25"/>
-      <c r="K22" s="27"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="26"/>
     </row>
     <row r="23" spans="2:12" ht="17.399999999999999" customHeight="1">
       <c r="B23" s="15"/>
     </row>
     <row r="24" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="23"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="22"/>
     </row>
     <row r="25" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="23"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="67"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="59"/>
       <c r="F26" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="65" t="s">
+      <c r="G26" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="66"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="24"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="23"/>
     </row>
     <row r="27" spans="2:12" ht="17.399999999999999" customHeight="1">
-      <c r="B27" s="78"/>
-      <c r="C27" s="80" t="s">
+      <c r="B27" s="56"/>
+      <c r="C27" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="81"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="46" t="s">
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="80" t="s">
+      <c r="G27" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="81"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="24"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="2:12" ht="25.8" customHeight="1">
       <c r="B28" s="11" t="s">
@@ -19987,13 +19980,13 @@
       <c r="I28" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="24"/>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="2:12" ht="17.399999999999999" customHeight="1">
       <c r="B29" s="18">
         <v>-35</v>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="41">
         <v>131.61557098881164</v>
       </c>
       <c r="D29" s="9">
@@ -20004,7 +19997,7 @@
         <f>C29*0.86</f>
         <v>113.18939105037801</v>
       </c>
-      <c r="F29" s="50">
+      <c r="F29" s="42">
         <v>86.922831307169446</v>
       </c>
       <c r="G29" s="13">
@@ -20019,13 +20012,13 @@
         <f>E29/F29</f>
         <v>1.3021825146305614</v>
       </c>
-      <c r="J29" s="25"/>
+      <c r="J29" s="24"/>
     </row>
     <row r="30" spans="2:12" ht="17.399999999999999" customHeight="1">
       <c r="B30" s="18">
         <v>-30</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="41">
         <v>164.20901967896489</v>
       </c>
       <c r="D30" s="9">
@@ -20036,7 +20029,7 @@
         <f t="shared" ref="E30:E34" si="6">C30*0.86</f>
         <v>141.21975692390981</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="42">
         <v>101.09717316522547</v>
       </c>
       <c r="G30" s="13">
@@ -20051,13 +20044,13 @@
         <f t="shared" ref="I30:I34" si="9">E30/F30</f>
         <v>1.3968714703141212</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="2:12" ht="17.399999999999999" customHeight="1">
       <c r="B31" s="18">
         <v>-25</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="41">
         <v>204.02791969312196</v>
       </c>
       <c r="D31" s="9">
@@ -20068,7 +20061,7 @@
         <f t="shared" si="6"/>
         <v>175.46401093608489</v>
       </c>
-      <c r="F31" s="50">
+      <c r="F31" s="42">
         <v>115.48807749140046</v>
       </c>
       <c r="G31" s="13">
@@ -20083,13 +20076,13 @@
         <f t="shared" si="9"/>
         <v>1.5193257585325237</v>
       </c>
-      <c r="J31" s="25"/>
+      <c r="J31" s="24"/>
     </row>
     <row r="32" spans="2:12" ht="17.399999999999999" customHeight="1">
       <c r="B32" s="18">
         <v>-20</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="41">
         <v>252.26117804739289</v>
       </c>
       <c r="D32" s="9">
@@ -20100,7 +20093,7 @@
         <f t="shared" si="6"/>
         <v>216.94461312075788</v>
       </c>
-      <c r="F32" s="50">
+      <c r="F32" s="42">
         <v>129.66642589805903</v>
       </c>
       <c r="G32" s="13">
@@ -20115,13 +20108,13 @@
         <f t="shared" si="9"/>
         <v>1.6730978093844824</v>
       </c>
-      <c r="J32" s="25"/>
+      <c r="J32" s="24"/>
     </row>
     <row r="33" spans="2:13" ht="17.399999999999999" customHeight="1">
       <c r="B33" s="18">
         <v>-15</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="41">
         <v>310.09770175788805</v>
       </c>
       <c r="D33" s="9">
@@ -20132,7 +20125,7 @@
         <f t="shared" si="6"/>
         <v>266.68402351178372</v>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="42">
         <v>143.20309999756583</v>
       </c>
       <c r="G33" s="13">
@@ -20147,13 +20140,13 @@
         <f t="shared" si="9"/>
         <v>1.8622782852907291</v>
       </c>
-      <c r="J33" s="25"/>
+      <c r="J33" s="24"/>
     </row>
     <row r="34" spans="2:13" ht="17.399999999999999" customHeight="1">
       <c r="B34" s="18">
         <v>-10</v>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="41">
         <v>378.72639784071748</v>
       </c>
       <c r="D34" s="9">
@@ -20164,7 +20157,7 @@
         <f t="shared" si="6"/>
         <v>325.70470214301702</v>
       </c>
-      <c r="F34" s="50">
+      <c r="F34" s="42">
         <v>155.66898140228545</v>
       </c>
       <c r="G34" s="13">
@@ -20179,75 +20172,75 @@
         <f t="shared" si="9"/>
         <v>2.0922903150584578</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="24"/>
     </row>
     <row r="35" spans="2:13" ht="17.399999999999999" customHeight="1">
       <c r="B35" s="15"/>
     </row>
     <row r="36" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B36" s="72" t="s">
+      <c r="B36" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="23"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="22"/>
       <c r="M36" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="37" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="23"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B38" s="77" t="s">
+      <c r="B38" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="65" t="s">
+      <c r="C38" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="66"/>
-      <c r="E38" s="67"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="59"/>
       <c r="F38" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="65" t="s">
+      <c r="G38" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="66"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="24"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="23"/>
     </row>
     <row r="39" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B39" s="78"/>
-      <c r="C39" s="80" t="s">
+      <c r="B39" s="56"/>
+      <c r="C39" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="81"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="46" t="s">
+      <c r="D39" s="61"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G39" s="80" t="s">
+      <c r="G39" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H39" s="81"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="24"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="23"/>
     </row>
     <row r="40" spans="2:13" ht="17.399999999999999" customHeight="1">
       <c r="B40" s="11" t="s">
@@ -20274,13 +20267,13 @@
       <c r="I40" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J40" s="24"/>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B41" s="21">
+      <c r="B41" s="17">
         <v>-35</v>
       </c>
-      <c r="C41" s="49">
+      <c r="C41" s="41">
         <v>136.62605259845111</v>
       </c>
       <c r="D41" s="9">
@@ -20291,7 +20284,7 @@
         <f>C41*0.86</f>
         <v>117.49840523466796</v>
       </c>
-      <c r="F41" s="50">
+      <c r="F41" s="42">
         <v>83.401558404979724</v>
       </c>
       <c r="G41" s="13">
@@ -20306,13 +20299,13 @@
         <f>E41/F41</f>
         <v>1.408827454567712</v>
       </c>
-      <c r="J41" s="25"/>
+      <c r="J41" s="24"/>
     </row>
     <row r="42" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B42" s="21">
+      <c r="B42" s="17">
         <v>-30</v>
       </c>
-      <c r="C42" s="49">
+      <c r="C42" s="41">
         <v>169.22368888471502</v>
       </c>
       <c r="D42" s="9">
@@ -20323,7 +20316,7 @@
         <f t="shared" ref="E42:E46" si="12">C42*0.86</f>
         <v>145.53237244085491</v>
       </c>
-      <c r="F42" s="50">
+      <c r="F42" s="42">
         <v>96.494113730493424</v>
       </c>
       <c r="G42" s="13">
@@ -20338,14 +20331,14 @@
         <f t="shared" ref="I42:I46" si="15">E42/F42</f>
         <v>1.5081994829998087</v>
       </c>
-      <c r="J42" s="25"/>
-      <c r="K42" s="27"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="26"/>
     </row>
     <row r="43" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B43" s="21">
+      <c r="B43" s="17">
         <v>-25</v>
       </c>
-      <c r="C43" s="49">
+      <c r="C43" s="41">
         <v>209.04796867497649</v>
       </c>
       <c r="D43" s="9">
@@ -20356,7 +20349,7 @@
         <f t="shared" si="12"/>
         <v>179.78125306047977</v>
       </c>
-      <c r="F43" s="50">
+      <c r="F43" s="42">
         <v>109.58515150782176</v>
       </c>
       <c r="G43" s="13">
@@ -20371,14 +20364,14 @@
         <f t="shared" si="15"/>
         <v>1.6405621618148485</v>
       </c>
-      <c r="J43" s="25"/>
-      <c r="K43" s="27"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="26"/>
     </row>
     <row r="44" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B44" s="21">
+      <c r="B44" s="17">
         <v>-20</v>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="41">
         <v>257.28779898534555</v>
       </c>
       <c r="D44" s="9">
@@ -20389,7 +20382,7 @@
         <f t="shared" si="12"/>
         <v>221.26750712739715</v>
       </c>
-      <c r="F44" s="50">
+      <c r="F44" s="42">
         <v>122.24555334932936</v>
       </c>
       <c r="G44" s="13">
@@ -20404,14 +20397,14 @@
         <f t="shared" si="15"/>
         <v>1.8100249953068011</v>
       </c>
-      <c r="J44" s="25"/>
-      <c r="K44" s="27"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="26"/>
     </row>
     <row r="45" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B45" s="21">
+      <c r="B45" s="17">
         <v>-15</v>
       </c>
-      <c r="C45" s="49">
+      <c r="C45" s="41">
         <v>315.13208683193255</v>
       </c>
       <c r="D45" s="9">
@@ -20422,7 +20415,7 @@
         <f t="shared" si="12"/>
         <v>271.013594675462</v>
       </c>
-      <c r="F45" s="50">
+      <c r="F45" s="42">
         <v>134.04620086738089</v>
       </c>
       <c r="G45" s="13">
@@ -20437,13 +20430,13 @@
         <f t="shared" si="15"/>
         <v>2.0217924336668842</v>
       </c>
-      <c r="J45" s="25"/>
+      <c r="J45" s="24"/>
     </row>
     <row r="46" spans="2:13" ht="17.399999999999999" customHeight="1">
-      <c r="B46" s="21">
+      <c r="B46" s="17">
         <v>-10</v>
       </c>
-      <c r="C46" s="49">
+      <c r="C46" s="41">
         <v>383.76973923084756</v>
       </c>
       <c r="D46" s="9">
@@ -20454,7 +20447,7 @@
         <f t="shared" si="12"/>
         <v>330.04197573852889</v>
       </c>
-      <c r="F46" s="50">
+      <c r="F46" s="42">
         <v>144.55797567434092</v>
       </c>
       <c r="G46" s="13">
@@ -20469,72 +20462,72 @@
         <f t="shared" si="15"/>
         <v>2.2831114934954879</v>
       </c>
-      <c r="J46" s="25"/>
+      <c r="J46" s="24"/>
     </row>
     <row r="47" spans="2:13" ht="18" customHeight="1">
       <c r="B47" s="15"/>
     </row>
     <row r="48" spans="2:13" ht="18" customHeight="1">
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="72"/>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="72"/>
-      <c r="I48" s="72"/>
-      <c r="J48" s="23"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="22"/>
     </row>
     <row r="49" spans="2:10" ht="18" customHeight="1">
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="23"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="22"/>
     </row>
     <row r="50" spans="2:10" ht="18" customHeight="1">
-      <c r="B50" s="77" t="s">
+      <c r="B50" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="65" t="s">
+      <c r="C50" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="66"/>
-      <c r="E50" s="67"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="59"/>
       <c r="F50" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="65" t="s">
+      <c r="G50" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="66"/>
-      <c r="I50" s="67"/>
-      <c r="J50" s="24"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="23"/>
     </row>
     <row r="51" spans="2:10" ht="18" customHeight="1">
-      <c r="B51" s="78"/>
-      <c r="C51" s="80" t="s">
+      <c r="B51" s="56"/>
+      <c r="C51" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="81"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="46" t="s">
+      <c r="D51" s="61"/>
+      <c r="E51" s="62"/>
+      <c r="F51" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="80" t="s">
+      <c r="G51" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H51" s="81"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="24"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="62"/>
+      <c r="J51" s="23"/>
     </row>
     <row r="52" spans="2:10" ht="18" customHeight="1">
       <c r="B52" s="11" t="s">
@@ -20561,13 +20554,13 @@
       <c r="I52" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J52" s="24"/>
+      <c r="J52" s="23"/>
     </row>
     <row r="53" spans="2:10" ht="18" customHeight="1">
       <c r="B53" s="18">
         <v>-35</v>
       </c>
-      <c r="C53" s="49">
+      <c r="C53" s="41">
         <v>141.63391938161868</v>
       </c>
       <c r="D53" s="9">
@@ -20578,7 +20571,7 @@
         <f>C53*0.86</f>
         <v>121.80517066819206</v>
       </c>
-      <c r="F53" s="50">
+      <c r="F53" s="42">
         <v>79.706066938427583</v>
       </c>
       <c r="G53" s="13">
@@ -20593,13 +20586,13 @@
         <f>E53/F53</f>
         <v>1.5281794140248541</v>
       </c>
-      <c r="J53" s="25"/>
+      <c r="J53" s="24"/>
     </row>
     <row r="54" spans="2:10" ht="18" customHeight="1">
       <c r="B54" s="18">
         <v>-30</v>
       </c>
-      <c r="C54" s="49">
+      <c r="C54" s="41">
         <v>174.23476242598781</v>
       </c>
       <c r="D54" s="9">
@@ -20610,7 +20603,7 @@
         <f t="shared" ref="E54:E58" si="18">C54*0.86</f>
         <v>149.84189568634952</v>
       </c>
-      <c r="F54" s="50">
+      <c r="F54" s="42">
         <v>91.658181281549048</v>
       </c>
       <c r="G54" s="13">
@@ -20625,13 +20618,13 @@
         <f t="shared" ref="I54:I58" si="21">E54/F54</f>
         <v>1.6347901910258933</v>
       </c>
-      <c r="J54" s="25"/>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="2:10" ht="18" customHeight="1">
       <c r="B55" s="18">
         <v>-25</v>
       </c>
-      <c r="C55" s="49">
+      <c r="C55" s="41">
         <v>214.06344115434814</v>
       </c>
       <c r="D55" s="9">
@@ -20642,7 +20635,7 @@
         <f t="shared" si="18"/>
         <v>184.0945593927394</v>
       </c>
-      <c r="F55" s="50">
+      <c r="F55" s="42">
         <v>103.3906980601809</v>
       </c>
       <c r="G55" s="13">
@@ -20657,13 +20650,13 @@
         <f t="shared" si="21"/>
         <v>1.7805717810859831</v>
       </c>
-      <c r="J55" s="25"/>
+      <c r="J55" s="24"/>
     </row>
     <row r="56" spans="2:10" ht="18" customHeight="1">
       <c r="B56" s="18">
         <v>-20</v>
       </c>
-      <c r="C56" s="49">
+      <c r="C56" s="41">
         <v>262.30886258280987</v>
       </c>
       <c r="D56" s="9">
@@ -20674,7 +20667,7 @@
         <f t="shared" si="18"/>
         <v>225.58562182121648</v>
       </c>
-      <c r="F56" s="50">
+      <c r="F56" s="42">
         <v>114.47449888668764</v>
       </c>
       <c r="G56" s="13">
@@ -20689,13 +20682,13 @@
         <f t="shared" si="21"/>
         <v>1.9706189938818772</v>
       </c>
-      <c r="J56" s="25"/>
+      <c r="J56" s="24"/>
     </row>
     <row r="57" spans="2:10" ht="18" customHeight="1">
       <c r="B57" s="18">
         <v>-15</v>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="41">
         <v>320.15993372748329</v>
       </c>
       <c r="D57" s="9">
@@ -20706,7 +20699,7 @@
         <f t="shared" si="18"/>
         <v>275.33754300563561</v>
       </c>
-      <c r="F57" s="50">
+      <c r="F57" s="42">
         <v>124.48046537343394</v>
       </c>
       <c r="G57" s="13">
@@ -20721,13 +20714,13 @@
         <f t="shared" si="21"/>
         <v>2.2118935865128675</v>
       </c>
-      <c r="J57" s="25"/>
+      <c r="J57" s="24"/>
     </row>
     <row r="58" spans="2:10" ht="18" customHeight="1">
       <c r="B58" s="18">
         <v>-10</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="41">
         <v>388.80556160447838</v>
       </c>
       <c r="D58" s="9">
@@ -20738,7 +20731,7 @@
         <f t="shared" si="18"/>
         <v>334.37278297985142</v>
       </c>
-      <c r="F58" s="50">
+      <c r="F58" s="42">
         <v>132.97947913278452</v>
       </c>
       <c r="G58" s="13">
@@ -20753,72 +20746,72 @@
         <f t="shared" si="21"/>
         <v>2.5144690380834538</v>
       </c>
-      <c r="J58" s="25"/>
+      <c r="J58" s="24"/>
     </row>
     <row r="59" spans="2:10" ht="18" customHeight="1">
       <c r="B59" s="15"/>
     </row>
     <row r="60" spans="2:10" ht="18" customHeight="1">
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="69"/>
-      <c r="D60" s="69"/>
-      <c r="E60" s="69"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="71"/>
-      <c r="J60" s="23"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="22"/>
     </row>
     <row r="61" spans="2:10" ht="18" customHeight="1">
-      <c r="B61" s="68" t="s">
+      <c r="B61" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="71"/>
-      <c r="J61" s="23"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="52"/>
+      <c r="E61" s="52"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="52"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="22"/>
     </row>
     <row r="62" spans="2:10" ht="18" customHeight="1">
-      <c r="B62" s="77" t="s">
+      <c r="B62" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="65" t="s">
+      <c r="C62" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="66"/>
-      <c r="E62" s="67"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="59"/>
       <c r="F62" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G62" s="65" t="s">
+      <c r="G62" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H62" s="66"/>
-      <c r="I62" s="67"/>
-      <c r="J62" s="24"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="59"/>
+      <c r="J62" s="23"/>
     </row>
     <row r="63" spans="2:10" ht="18" customHeight="1">
-      <c r="B63" s="78"/>
-      <c r="C63" s="80" t="s">
+      <c r="B63" s="56"/>
+      <c r="C63" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D63" s="81"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="46" t="s">
+      <c r="D63" s="61"/>
+      <c r="E63" s="62"/>
+      <c r="F63" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G63" s="80" t="s">
+      <c r="G63" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="81"/>
-      <c r="I63" s="82"/>
-      <c r="J63" s="24"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="62"/>
+      <c r="J63" s="23"/>
     </row>
     <row r="64" spans="2:10" ht="18" customHeight="1">
       <c r="B64" s="11" t="s">
@@ -20845,13 +20838,13 @@
       <c r="I64" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J64" s="24"/>
+      <c r="J64" s="23"/>
     </row>
     <row r="65" spans="2:11" ht="18" customHeight="1">
       <c r="B65" s="18">
         <v>-35</v>
       </c>
-      <c r="C65" s="49">
+      <c r="C65" s="41">
         <v>146.63917133831444</v>
       </c>
       <c r="D65" s="9">
@@ -20862,7 +20855,7 @@
         <f>C65*0.86</f>
         <v>126.10968735095042</v>
       </c>
-      <c r="F65" s="50">
+      <c r="F65" s="42">
         <v>75.827089239062076</v>
       </c>
       <c r="G65" s="13">
@@ -20877,13 +20870,13 @@
         <f>E65/F65</f>
         <v>1.6631218291046497</v>
       </c>
-      <c r="J65" s="25"/>
+      <c r="J65" s="24"/>
     </row>
     <row r="66" spans="2:11" ht="18" customHeight="1">
       <c r="B66" s="18">
         <v>-30</v>
       </c>
-      <c r="C66" s="49">
+      <c r="C66" s="41">
         <v>179.24224030278316</v>
       </c>
       <c r="D66" s="9">
@@ -20894,7 +20887,7 @@
         <f t="shared" ref="E66:E70" si="24">C66*0.86</f>
         <v>154.14832666039351</v>
       </c>
-      <c r="F66" s="50">
+      <c r="F66" s="42">
         <v>86.580108149941424</v>
       </c>
       <c r="G66" s="13">
@@ -20909,14 +20902,14 @@
         <f t="shared" ref="I66:I70" si="27">E66/F66</f>
         <v>1.7804127293700753</v>
       </c>
-      <c r="J66" s="25"/>
-      <c r="K66" s="27"/>
+      <c r="J66" s="24"/>
+      <c r="K66" s="26"/>
     </row>
     <row r="67" spans="2:11" ht="18" customHeight="1">
       <c r="B67" s="18">
         <v>-25</v>
       </c>
-      <c r="C67" s="49">
+      <c r="C67" s="41">
         <v>219.07433713123692</v>
       </c>
       <c r="D67" s="9">
@@ -20927,7 +20920,7 @@
         <f t="shared" si="24"/>
         <v>188.40392993286375</v>
       </c>
-      <c r="F67" s="50">
+      <c r="F67" s="42">
         <v>96.895449480026912</v>
       </c>
       <c r="G67" s="13">
@@ -20942,13 +20935,13 @@
         <f t="shared" si="27"/>
         <v>1.944404313555504</v>
       </c>
-      <c r="J67" s="25"/>
+      <c r="J67" s="24"/>
     </row>
     <row r="68" spans="2:11" ht="18" customHeight="1">
       <c r="B68" s="18">
         <v>-20</v>
       </c>
-      <c r="C68" s="49">
+      <c r="C68" s="41">
         <v>267.32436883978573</v>
       </c>
       <c r="D68" s="9">
@@ -20959,7 +20952,7 @@
         <f t="shared" si="24"/>
         <v>229.89895720221574</v>
       </c>
-      <c r="F68" s="50">
+      <c r="F68" s="42">
         <v>106.34399484168287</v>
       </c>
       <c r="G68" s="13">
@@ -20974,13 +20967,13 @@
         <f t="shared" si="27"/>
         <v>2.1618424015805728</v>
       </c>
-      <c r="J68" s="25"/>
+      <c r="J68" s="24"/>
     </row>
     <row r="69" spans="2:11" ht="18" customHeight="1">
       <c r="B69" s="18">
         <v>-15</v>
       </c>
-      <c r="C69" s="49">
+      <c r="C69" s="41">
         <v>325.18124244453998</v>
       </c>
       <c r="D69" s="9">
@@ -20991,7 +20984,7 @@
         <f t="shared" si="24"/>
         <v>279.65586850230437</v>
       </c>
-      <c r="F69" s="50">
+      <c r="F69" s="42">
         <v>114.49662584727415</v>
       </c>
       <c r="G69" s="13">
@@ -21006,13 +20999,13 @@
         <f t="shared" si="27"/>
         <v>2.4424813083604264</v>
       </c>
-      <c r="J69" s="25"/>
+      <c r="J69" s="24"/>
     </row>
     <row r="70" spans="2:11" ht="18" customHeight="1">
       <c r="B70" s="18">
         <v>-10</v>
       </c>
-      <c r="C70" s="49">
+      <c r="C70" s="41">
         <v>393.83386496160966</v>
       </c>
       <c r="D70" s="9">
@@ -21023,7 +21016,7 @@
         <f t="shared" si="24"/>
         <v>338.69712386698433</v>
       </c>
-      <c r="F70" s="50">
+      <c r="F70" s="42">
         <v>120.92422410916532</v>
       </c>
       <c r="G70" s="13">
@@ -21038,94 +21031,94 @@
         <f t="shared" si="27"/>
         <v>2.8009038417416079</v>
       </c>
-      <c r="J70" s="25"/>
+      <c r="J70" s="24"/>
     </row>
     <row r="71" spans="2:11" ht="18" customHeight="1">
-      <c r="B71" s="32"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="43"/>
-      <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="25"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="24"/>
     </row>
     <row r="72" spans="2:11" ht="18" customHeight="1">
-      <c r="B72" s="32"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="44"/>
-      <c r="I72" s="44"/>
-      <c r="J72" s="25"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="24"/>
     </row>
     <row r="73" spans="2:11" ht="18" customHeight="1">
-      <c r="B73" s="72" t="s">
+      <c r="B73" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="72"/>
-      <c r="D73" s="72"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="72"/>
-      <c r="H73" s="72"/>
-      <c r="I73" s="72"/>
-      <c r="J73" s="25"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="24"/>
     </row>
     <row r="74" spans="2:11" ht="18" customHeight="1">
-      <c r="B74" s="68" t="s">
+      <c r="B74" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C74" s="69"/>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="70"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="25"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="24"/>
     </row>
     <row r="75" spans="2:11" ht="18" customHeight="1">
-      <c r="B75" s="77" t="s">
+      <c r="B75" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C75" s="65" t="s">
+      <c r="C75" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D75" s="66"/>
-      <c r="E75" s="67"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="59"/>
       <c r="F75" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G75" s="65" t="s">
+      <c r="G75" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H75" s="66"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="25"/>
+      <c r="H75" s="58"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="24"/>
     </row>
     <row r="76" spans="2:11" ht="18" customHeight="1">
-      <c r="B76" s="78"/>
-      <c r="C76" s="80" t="s">
+      <c r="B76" s="56"/>
+      <c r="C76" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D76" s="81"/>
-      <c r="E76" s="82"/>
-      <c r="F76" s="46" t="s">
+      <c r="D76" s="61"/>
+      <c r="E76" s="62"/>
+      <c r="F76" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G76" s="80" t="s">
+      <c r="G76" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H76" s="81"/>
-      <c r="I76" s="82"/>
-      <c r="J76" s="25"/>
+      <c r="H76" s="61"/>
+      <c r="I76" s="62"/>
+      <c r="J76" s="24"/>
     </row>
     <row r="77" spans="2:11" ht="18" customHeight="1">
-      <c r="B77" s="47" t="s">
+      <c r="B77" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C77" s="10" t="s">
@@ -21134,28 +21127,28 @@
       <c r="D77" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E77" s="47" t="s">
+      <c r="E77" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G77" s="47" t="s">
+      <c r="G77" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H77" s="47" t="s">
+      <c r="H77" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I77" s="47" t="s">
+      <c r="I77" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J77" s="25"/>
+      <c r="J77" s="24"/>
     </row>
     <row r="78" spans="2:11" ht="18" customHeight="1">
-      <c r="B78" s="51" t="s">
+      <c r="B78" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C78" s="48">
+      <c r="C78" s="40">
         <v>215</v>
       </c>
       <c r="D78" s="9">
@@ -21166,7 +21159,7 @@
         <f>C78*0.86</f>
         <v>184.9</v>
       </c>
-      <c r="F78" s="50">
+      <c r="F78" s="42">
         <f>C78/G78</f>
         <v>125.73099415204679</v>
       </c>
@@ -21182,27 +21175,62 @@
         <f>G78*0.86</f>
         <v>1.4705999999999999</v>
       </c>
-      <c r="J78" s="25"/>
+      <c r="J78" s="24"/>
     </row>
     <row r="79" spans="2:11" ht="18" customHeight="1">
-      <c r="B79" s="76" t="s">
+      <c r="B79" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="C79" s="76"/>
-      <c r="D79" s="76"/>
-      <c r="E79" s="76"/>
-      <c r="F79" s="76"/>
-      <c r="G79" s="76"/>
-      <c r="H79" s="76"/>
-      <c r="I79" s="76"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="73"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="73"/>
+      <c r="I79" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C39:E39"/>
     <mergeCell ref="B75:B76"/>
     <mergeCell ref="C76:E76"/>
     <mergeCell ref="G76:I76"/>
@@ -21219,46 +21247,11 @@
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="B37:I37"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G7:I7"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.511811023622047" right="0.511811023622047" top="0.35433070866141703" bottom="0.35433070866141703" header="0.31496062992126" footer="0.31496062992126"/>
@@ -21286,69 +21279,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="23"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="23"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="24"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="23"/>
     </row>
     <row r="4" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B4" s="78"/>
-      <c r="C4" s="80" t="s">
+      <c r="B4" s="56"/>
+      <c r="C4" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="46" t="s">
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="80" t="s">
+      <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="81"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="24"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="19" t="s">
@@ -21357,28 +21350,28 @@
       <c r="D5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B6" s="21">
+      <c r="B6" s="17">
         <v>-35</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="41">
         <v>98.203782559539377</v>
       </c>
       <c r="D6" s="9">
@@ -21389,7 +21382,7 @@
         <f>C6*0.86</f>
         <v>84.455253001203857</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="41">
         <v>63.445349604334389</v>
       </c>
       <c r="G6" s="13">
@@ -21404,14 +21397,14 @@
         <f t="shared" ref="I6:I11" si="2">E6/F6</f>
         <v>1.3311496197576966</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="L6" s="26"/>
+      <c r="J6" s="24"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B7" s="21">
+      <c r="B7" s="17">
         <v>-30</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="41">
         <v>123.51653978167045</v>
       </c>
       <c r="D7" s="9">
@@ -21422,7 +21415,7 @@
         <f t="shared" ref="E7:E11" si="4">C7*0.86</f>
         <v>106.22422421223658</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="41">
         <v>74.125656318397475</v>
       </c>
       <c r="G7" s="13">
@@ -21437,14 +21430,14 @@
         <f t="shared" si="2"/>
         <v>1.4330291222780371</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="L7" s="26"/>
+      <c r="J7" s="24"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B8" s="21">
+      <c r="B8" s="17">
         <v>-25</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="41">
         <v>154.44069829240473</v>
       </c>
       <c r="D8" s="9">
@@ -21455,7 +21448,7 @@
         <f t="shared" si="4"/>
         <v>132.81900053146808</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="41">
         <v>85.111416100694257</v>
       </c>
       <c r="G8" s="13">
@@ -21470,14 +21463,14 @@
         <f t="shared" si="2"/>
         <v>1.560530967718027</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="L8" s="26"/>
+      <c r="J8" s="24"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B9" s="21">
+      <c r="B9" s="17">
         <v>-20</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="41">
         <v>191.89973470425559</v>
       </c>
       <c r="D9" s="9">
@@ -21488,7 +21481,7 @@
         <f t="shared" si="4"/>
         <v>165.0337718456598</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="41">
         <v>96.10105804447673</v>
       </c>
       <c r="G9" s="13">
@@ -21503,14 +21496,14 @@
         <f t="shared" si="2"/>
         <v>1.7172940153195835</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="27"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="26"/>
     </row>
     <row r="10" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B10" s="21">
+      <c r="B10" s="17">
         <v>-15</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="41">
         <v>236.81712562973669</v>
       </c>
       <c r="D10" s="9">
@@ -21521,7 +21514,7 @@
         <f t="shared" si="4"/>
         <v>203.66272804157356</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="41">
         <v>106.79301124299701</v>
       </c>
       <c r="G10" s="13">
@@ -21536,14 +21529,14 @@
         <f t="shared" si="2"/>
         <v>1.9070791774768765</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="27"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B11" s="21">
+      <c r="B11" s="17">
         <v>-10</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="41">
         <v>290.11634768136128</v>
       </c>
       <c r="D11" s="9">
@@ -21554,7 +21547,7 @@
         <f t="shared" si="4"/>
         <v>249.50005900597068</v>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="41">
         <v>116.88570478950706</v>
       </c>
       <c r="G11" s="13">
@@ -21569,82 +21562,82 @@
         <f t="shared" si="2"/>
         <v>2.134564354599918</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="27"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="26"/>
     </row>
     <row r="12" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="27"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="26"/>
     </row>
     <row r="13" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="23"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="23"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="22"/>
     </row>
     <row r="15" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="66"/>
-      <c r="E15" s="67"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59"/>
       <c r="F15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="65" t="s">
+      <c r="G15" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="66"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="24"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B16" s="78"/>
-      <c r="C16" s="80" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="46" t="s">
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="80" t="s">
+      <c r="G16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="24"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="2:13" ht="15.9" customHeight="1">
       <c r="B17" s="11" t="s">
@@ -21671,13 +21664,13 @@
       <c r="I17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="24"/>
+      <c r="J17" s="23"/>
     </row>
     <row r="18" spans="2:13" ht="15.9" customHeight="1">
       <c r="B18" s="17">
         <v>-35</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="41">
         <v>103.21395514014671</v>
       </c>
       <c r="D18" s="9">
@@ -21688,7 +21681,7 @@
         <f>C18*0.86</f>
         <v>88.764001420526171</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="41">
         <v>61.086632057065032</v>
       </c>
       <c r="G18" s="13">
@@ -21703,13 +21696,13 @@
         <f t="shared" ref="I18:I23" si="7">E18/F18</f>
         <v>1.45308389792395</v>
       </c>
-      <c r="J18" s="25"/>
+      <c r="J18" s="24"/>
     </row>
     <row r="19" spans="2:13" ht="15.9" customHeight="1">
       <c r="B19" s="17">
         <v>-30</v>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="41">
         <v>128.53072691342854</v>
       </c>
       <c r="D19" s="9">
@@ -21720,7 +21713,7 @@
         <f t="shared" ref="E19:E23" si="9">C19*0.86</f>
         <v>110.53642514554853</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="41">
         <v>71.047913721652364</v>
       </c>
       <c r="G19" s="13">
@@ -21735,13 +21728,13 @@
         <f t="shared" si="7"/>
         <v>1.5558011397576303</v>
       </c>
-      <c r="J19" s="25"/>
+      <c r="J19" s="24"/>
     </row>
     <row r="20" spans="2:13" ht="15.9" customHeight="1">
       <c r="B20" s="17">
         <v>-25</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="41">
         <v>159.45982599419241</v>
       </c>
       <c r="D20" s="9">
@@ -21752,7 +21745,7 @@
         <f t="shared" si="9"/>
         <v>137.13545035500547</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="41">
         <v>81.161388677788182</v>
       </c>
       <c r="G20" s="13">
@@ -21767,13 +21760,13 @@
         <f t="shared" si="7"/>
         <v>1.6896636761531407</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="24"/>
     </row>
     <row r="21" spans="2:13" ht="15.9" customHeight="1">
       <c r="B21" s="17">
         <v>-20</v>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="41">
         <v>196.92472899495169</v>
       </c>
       <c r="D21" s="9">
@@ -21784,7 +21777,7 @@
         <f t="shared" si="9"/>
         <v>169.35526693565845</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="41">
         <v>91.12548601872453</v>
       </c>
       <c r="G21" s="13">
@@ -21799,13 +21792,13 @@
         <f t="shared" si="7"/>
         <v>1.8584841007142525</v>
       </c>
-      <c r="J21" s="25"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="2:13" ht="15.9" customHeight="1">
       <c r="B22" s="17">
         <v>-15</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="41">
         <v>241.84891252822004</v>
       </c>
       <c r="D22" s="9">
@@ -21816,7 +21809,7 @@
         <f t="shared" si="9"/>
         <v>207.99006477426923</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="41">
         <v>100.63863483771348</v>
       </c>
       <c r="G22" s="13">
@@ -21831,13 +21824,13 @@
         <f t="shared" si="7"/>
         <v>2.0667019689770942</v>
       </c>
-      <c r="J22" s="25"/>
+      <c r="J22" s="24"/>
     </row>
     <row r="23" spans="2:13" ht="15.9" customHeight="1">
       <c r="B23" s="17">
         <v>-10</v>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="41">
         <v>295.15585320651076</v>
       </c>
       <c r="D23" s="9">
@@ -21848,7 +21841,7 @@
         <f t="shared" si="9"/>
         <v>253.83403375759926</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="41">
         <v>109.39926422800703</v>
       </c>
       <c r="G23" s="13">
@@ -21863,75 +21856,75 @@
         <f t="shared" si="7"/>
         <v>2.3202535734478538</v>
       </c>
-      <c r="J23" s="25"/>
+      <c r="J23" s="24"/>
     </row>
     <row r="24" spans="2:13" ht="15.9" customHeight="1">
       <c r="B24" s="15"/>
     </row>
     <row r="25" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="23"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="22"/>
       <c r="M25" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="23"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="67"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="59"/>
       <c r="F27" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="65" t="s">
+      <c r="G27" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="66"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="24"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B28" s="78"/>
-      <c r="C28" s="80" t="s">
+      <c r="B28" s="56"/>
+      <c r="C28" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="81"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="46" t="s">
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="80" t="s">
+      <c r="G28" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H28" s="81"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="24"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="2:13" ht="15.9" customHeight="1">
       <c r="B29" s="11" t="s">
@@ -21958,13 +21951,13 @@
       <c r="I29" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="24"/>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="2:13" ht="15.9" customHeight="1">
       <c r="B30" s="17">
         <v>-35</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="41">
         <v>108.22209666949459</v>
       </c>
       <c r="D30" s="9">
@@ -21975,7 +21968,7 @@
         <f>C30*0.86</f>
         <v>93.071003135765352</v>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="41">
         <v>58.611992207973564</v>
       </c>
       <c r="G30" s="13">
@@ -21990,13 +21983,13 @@
         <f t="shared" ref="I30:I35" si="12">E30/F30</f>
         <v>1.587917414673784</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="2:13" ht="15.9" customHeight="1">
       <c r="B31" s="17">
         <v>-30</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="41">
         <v>133.54212113370886</v>
       </c>
       <c r="D31" s="9">
@@ -22007,7 +22000,7 @@
         <f t="shared" ref="E31:E35" si="14">C31*0.86</f>
         <v>114.84622417498962</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="41">
         <v>67.813028320455288</v>
       </c>
       <c r="G31" s="13">
@@ -22022,14 +22015,14 @@
         <f t="shared" si="12"/>
         <v>1.6935716781777628</v>
       </c>
-      <c r="J31" s="25"/>
-      <c r="K31" s="27"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="26"/>
     </row>
     <row r="32" spans="2:13" ht="15.9" customHeight="1">
       <c r="B32" s="17">
         <v>-25</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="41">
         <v>164.47539892428406</v>
       </c>
       <c r="D32" s="9">
@@ -22040,7 +22033,7 @@
         <f t="shared" si="14"/>
         <v>141.44884307488428</v>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="41">
         <v>77.012997947800315</v>
       </c>
       <c r="G32" s="13">
@@ -22055,14 +22048,14 @@
         <f t="shared" si="12"/>
         <v>1.8366879207943418</v>
       </c>
-      <c r="J32" s="25"/>
-      <c r="K32" s="27"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="26"/>
     </row>
     <row r="33" spans="2:11" ht="15.9" customHeight="1">
       <c r="B33" s="17">
         <v>-20</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="41">
         <v>201.94540665373353</v>
       </c>
       <c r="D33" s="9">
@@ -22073,7 +22066,7 @@
         <f t="shared" si="14"/>
         <v>173.67304972221083</v>
       </c>
-      <c r="F33" s="49">
+      <c r="F33" s="41">
         <v>85.910330183260697</v>
       </c>
       <c r="G33" s="13">
@@ -22088,14 +22081,14 @@
         <f t="shared" si="12"/>
         <v>2.0215618931010741</v>
       </c>
-      <c r="J33" s="25"/>
-      <c r="K33" s="27"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="26"/>
     </row>
     <row r="34" spans="2:11" ht="15.9" customHeight="1">
       <c r="B34" s="17">
         <v>-15</v>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="41">
         <v>246.87562093457089</v>
       </c>
       <c r="D34" s="9">
@@ -22106,7 +22099,7 @@
         <f t="shared" si="14"/>
         <v>212.31303400373096</v>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="41">
         <v>94.203454120088495</v>
       </c>
       <c r="G34" s="13">
@@ -22121,13 +22114,13 @@
         <f t="shared" si="12"/>
         <v>2.2537712230071625</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="24"/>
     </row>
     <row r="35" spans="2:11" ht="15.9" customHeight="1">
       <c r="B35" s="17">
         <v>-10</v>
       </c>
-      <c r="C35" s="49">
+      <c r="C35" s="41">
         <v>300.1895183793095</v>
       </c>
       <c r="D35" s="9">
@@ -22138,7 +22131,7 @@
         <f t="shared" si="14"/>
         <v>258.16298580620617</v>
       </c>
-      <c r="F35" s="49">
+      <c r="F35" s="41">
         <v>101.59079885153571</v>
       </c>
       <c r="G35" s="13">
@@ -22153,72 +22146,72 @@
         <f t="shared" si="12"/>
         <v>2.54120440753187</v>
       </c>
-      <c r="J35" s="25"/>
+      <c r="J35" s="24"/>
     </row>
     <row r="36" spans="2:11" ht="15.9" customHeight="1">
       <c r="B36" s="15"/>
     </row>
     <row r="37" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B37" s="92" t="s">
+      <c r="B37" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="23"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="23"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="39" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="66"/>
-      <c r="E39" s="67"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="65" t="s">
+      <c r="G39" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="66"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="24"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="23"/>
     </row>
     <row r="40" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B40" s="78"/>
-      <c r="C40" s="80" t="s">
+      <c r="B40" s="56"/>
+      <c r="C40" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="46" t="s">
+      <c r="D40" s="61"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="80" t="s">
+      <c r="G40" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="81"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="24"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="2:11" ht="15.9" customHeight="1">
       <c r="B41" s="11" t="s">
@@ -22245,13 +22238,13 @@
       <c r="I41" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="24"/>
+      <c r="J41" s="23"/>
     </row>
     <row r="42" spans="2:11" ht="15.9" customHeight="1">
       <c r="B42" s="18">
         <v>-35</v>
       </c>
-      <c r="C42" s="49">
+      <c r="C42" s="41">
         <v>113.22820714758288</v>
       </c>
       <c r="D42" s="9">
@@ -22262,7 +22255,7 @@
         <f>C42*0.86</f>
         <v>97.376258146921273</v>
       </c>
-      <c r="F42" s="49">
+      <c r="F42" s="41">
         <v>56.014917031147441</v>
       </c>
       <c r="G42" s="13">
@@ -22277,13 +22270,13 @@
         <f t="shared" ref="I42:I47" si="17">E42/F42</f>
         <v>1.7383986857067841</v>
       </c>
-      <c r="J42" s="25"/>
+      <c r="J42" s="24"/>
     </row>
     <row r="43" spans="2:11" ht="15.9" customHeight="1">
       <c r="B43" s="18">
         <v>-30</v>
       </c>
-      <c r="C43" s="49">
+      <c r="C43" s="41">
         <v>138.55072244251144</v>
       </c>
       <c r="D43" s="9">
@@ -22294,7 +22287,7 @@
         <f t="shared" ref="E43:E47" si="19">C43*0.86</f>
         <v>119.15362130055983</v>
       </c>
-      <c r="F43" s="49">
+      <c r="F43" s="41">
         <v>64.414487088893722</v>
       </c>
       <c r="G43" s="13">
@@ -22309,13 +22302,13 @@
         <f t="shared" si="17"/>
         <v>1.8497953905326396</v>
       </c>
-      <c r="J43" s="25"/>
+      <c r="J43" s="24"/>
     </row>
     <row r="44" spans="2:11" ht="15.9" customHeight="1">
       <c r="B44" s="18">
         <v>-25</v>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="41">
         <v>169.48741708267971</v>
       </c>
       <c r="D44" s="9">
@@ -22326,7 +22319,7 @@
         <f t="shared" si="19"/>
         <v>145.75917869110455</v>
       </c>
-      <c r="F44" s="49">
+      <c r="F44" s="41">
         <v>72.659730884818146</v>
       </c>
       <c r="G44" s="13">
@@ -22341,13 +22334,13 @@
         <f t="shared" si="17"/>
         <v>2.0060517279119203</v>
       </c>
-      <c r="J44" s="25"/>
+      <c r="J44" s="24"/>
     </row>
     <row r="45" spans="2:11" ht="15.9" customHeight="1">
       <c r="B45" s="18">
         <v>-20</v>
       </c>
-      <c r="C45" s="49">
+      <c r="C45" s="41">
         <v>206.96176768060116</v>
       </c>
       <c r="D45" s="9">
@@ -22358,7 +22351,7 @@
         <f t="shared" si="19"/>
         <v>177.98712020531698</v>
       </c>
-      <c r="F45" s="49">
+      <c r="F45" s="41">
         <v>80.449077512172735</v>
       </c>
       <c r="G45" s="13">
@@ -22373,13 +22366,13 @@
         <f t="shared" si="17"/>
         <v>2.212419653642216</v>
       </c>
-      <c r="J45" s="25"/>
+      <c r="J45" s="24"/>
     </row>
     <row r="46" spans="2:11" ht="15.9" customHeight="1">
       <c r="B46" s="18">
         <v>-15</v>
       </c>
-      <c r="C46" s="49">
+      <c r="C46" s="41">
         <v>251.89725084878938</v>
       </c>
       <c r="D46" s="9">
@@ -22390,7 +22383,7 @@
         <f t="shared" si="19"/>
         <v>216.63163572995887</v>
       </c>
-      <c r="F46" s="49">
+      <c r="F46" s="41">
         <v>87.480956064209494</v>
       </c>
       <c r="G46" s="13">
@@ -22405,13 +22398,13 @@
         <f t="shared" si="17"/>
         <v>2.4763290832230394</v>
       </c>
-      <c r="J46" s="25"/>
+      <c r="J46" s="24"/>
     </row>
     <row r="47" spans="2:11" ht="15.9" customHeight="1">
       <c r="B47" s="18">
         <v>-10</v>
       </c>
-      <c r="C47" s="49">
+      <c r="C47" s="41">
         <v>305.21734319975764</v>
       </c>
       <c r="D47" s="9">
@@ -22422,7 +22415,7 @@
         <f t="shared" si="19"/>
         <v>262.48691515179155</v>
       </c>
-      <c r="F47" s="49">
+      <c r="F47" s="41">
         <v>93.453795634180565</v>
       </c>
       <c r="G47" s="13">
@@ -22437,79 +22430,75 @@
         <f t="shared" si="17"/>
         <v>2.8087346626270939</v>
       </c>
-      <c r="J47" s="25"/>
+      <c r="J47" s="24"/>
     </row>
     <row r="48" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B48" s="34"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="33"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="35"/>
     </row>
     <row r="49" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B49" s="72" t="s">
+      <c r="B49" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="79"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="72"/>
-      <c r="I49" s="72"/>
-      <c r="J49" s="23"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="49"/>
+      <c r="J49" s="22"/>
     </row>
     <row r="50" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="69"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="23"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="22"/>
     </row>
     <row r="51" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B51" s="77" t="s">
+      <c r="B51" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="C51" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="66"/>
-      <c r="E51" s="67"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="59"/>
       <c r="F51" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G51" s="65" t="s">
+      <c r="G51" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H51" s="66"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="24"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="23"/>
     </row>
     <row r="52" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B52" s="78"/>
-      <c r="C52" s="80" t="s">
+      <c r="B52" s="56"/>
+      <c r="C52" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="46" t="s">
+      <c r="D52" s="61"/>
+      <c r="E52" s="62"/>
+      <c r="F52" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="80" t="s">
+      <c r="G52" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H52" s="81"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="24"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="62"/>
+      <c r="J52" s="23"/>
     </row>
     <row r="53" spans="2:11" ht="15.9" customHeight="1">
       <c r="B53" s="11" t="s">
@@ -22536,13 +22525,13 @@
       <c r="I53" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J53" s="24"/>
+      <c r="J53" s="23"/>
     </row>
     <row r="54" spans="2:11" ht="15.9" customHeight="1">
       <c r="B54" s="17">
         <v>-35</v>
       </c>
-      <c r="C54" s="49">
+      <c r="C54" s="41">
         <v>118.23228657441166</v>
       </c>
       <c r="D54" s="9">
@@ -22553,7 +22542,7 @@
         <f>C54*0.86</f>
         <v>101.67976645399402</v>
       </c>
-      <c r="F54" s="49">
+      <c r="F54" s="41">
         <v>53.288893500674192</v>
       </c>
       <c r="G54" s="13">
@@ -22568,13 +22557,13 @@
         <f t="shared" ref="I54:I59" si="22">E54/F54</f>
         <v>1.9080855272911157</v>
       </c>
-      <c r="J54" s="25"/>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="2:11" ht="15.9" customHeight="1">
       <c r="B55" s="17">
         <v>-30</v>
       </c>
-      <c r="C55" s="49">
+      <c r="C55" s="41">
         <v>143.55653083983623</v>
       </c>
       <c r="D55" s="9">
@@ -22585,7 +22574,7 @@
         <f t="shared" ref="E55:E59" si="24">C55*0.86</f>
         <v>123.45861652225915</v>
       </c>
-      <c r="F55" s="49">
+      <c r="F55" s="41">
         <v>60.845777001055183</v>
       </c>
       <c r="G55" s="13">
@@ -22600,14 +22589,14 @@
         <f t="shared" si="22"/>
         <v>2.0290416624989134</v>
       </c>
-      <c r="J55" s="25"/>
-      <c r="K55" s="27"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="26"/>
     </row>
     <row r="56" spans="2:11" ht="15.9" customHeight="1">
       <c r="B56" s="17">
         <v>-25</v>
       </c>
-      <c r="C56" s="49">
+      <c r="C56" s="41">
         <v>174.49588046937936</v>
       </c>
       <c r="D56" s="9">
@@ -22618,7 +22607,7 @@
         <f t="shared" si="24"/>
         <v>150.06645720366623</v>
       </c>
-      <c r="F56" s="49">
+      <c r="F56" s="41">
         <v>68.095074462929205</v>
       </c>
       <c r="G56" s="13">
@@ -22633,13 +22622,13 @@
         <f t="shared" si="22"/>
         <v>2.2037784434080039</v>
       </c>
-      <c r="J56" s="25"/>
+      <c r="J56" s="24"/>
     </row>
     <row r="57" spans="2:11" ht="15.9" customHeight="1">
       <c r="B57" s="17">
         <v>-20</v>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="41">
         <v>211.97381207555452</v>
       </c>
       <c r="D57" s="9">
@@ -22650,7 +22639,7 @@
         <f t="shared" si="24"/>
         <v>182.2974783849769</v>
       </c>
-      <c r="F57" s="49">
+      <c r="F57" s="41">
         <v>74.735214979548118</v>
       </c>
       <c r="G57" s="13">
@@ -22665,13 +22654,13 @@
         <f t="shared" si="22"/>
         <v>2.4392447179668117</v>
       </c>
-      <c r="J57" s="25"/>
+      <c r="J57" s="24"/>
     </row>
     <row r="58" spans="2:11" ht="15.9" customHeight="1">
       <c r="B58" s="17">
         <v>-15</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="41">
         <v>256.91380227087524</v>
       </c>
       <c r="D58" s="9">
@@ -22682,7 +22671,7 @@
         <f t="shared" si="24"/>
         <v>220.94586995295271</v>
       </c>
-      <c r="F58" s="49">
+      <c r="F58" s="41">
         <v>80.464627644164096</v>
       </c>
       <c r="G58" s="13">
@@ -22697,13 +22686,13 @@
         <f t="shared" si="22"/>
         <v>2.7458757521383665</v>
       </c>
-      <c r="J58" s="25"/>
+      <c r="J58" s="24"/>
     </row>
     <row r="59" spans="2:11" ht="15.9" customHeight="1">
       <c r="B59" s="17">
         <v>-10</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="41">
         <v>310.23932766785492</v>
       </c>
       <c r="D59" s="9">
@@ -22714,7 +22703,7 @@
         <f t="shared" si="24"/>
         <v>266.80582179435521</v>
       </c>
-      <c r="F59" s="49">
+      <c r="F59" s="41">
         <v>84.981741550029142</v>
       </c>
       <c r="G59" s="13">
@@ -22729,79 +22718,79 @@
         <f t="shared" si="22"/>
         <v>3.1395664165965038</v>
       </c>
-      <c r="J59" s="25"/>
+      <c r="J59" s="24"/>
     </row>
     <row r="60" spans="2:11" ht="27" customHeight="1"/>
     <row r="61" spans="2:11" ht="12" customHeight="1">
-      <c r="B61" s="76"/>
-      <c r="C61" s="76"/>
-      <c r="D61" s="76"/>
-      <c r="E61" s="76"/>
-      <c r="F61" s="94"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="76"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" spans="2:11" ht="18" customHeight="1">
-      <c r="B62" s="72" t="s">
+      <c r="B62" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
     </row>
     <row r="63" spans="2:11" ht="18" customHeight="1">
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="71"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="54"/>
     </row>
     <row r="64" spans="2:11" ht="18" customHeight="1">
-      <c r="B64" s="77" t="s">
+      <c r="B64" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="65" t="s">
+      <c r="C64" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="66"/>
-      <c r="E64" s="67"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="59"/>
       <c r="F64" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="65" t="s">
+      <c r="G64" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H64" s="66"/>
-      <c r="I64" s="67"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="59"/>
     </row>
     <row r="65" spans="2:9" ht="18" customHeight="1">
-      <c r="B65" s="78"/>
-      <c r="C65" s="80" t="s">
+      <c r="B65" s="56"/>
+      <c r="C65" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D65" s="81"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="46" t="s">
+      <c r="D65" s="61"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G65" s="80" t="s">
+      <c r="G65" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H65" s="81"/>
-      <c r="I65" s="82"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="62"/>
     </row>
     <row r="66" spans="2:9" ht="18" customHeight="1">
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C66" s="10" t="s">
@@ -22810,27 +22799,27 @@
       <c r="D66" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="47" t="s">
+      <c r="E66" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G66" s="47" t="s">
+      <c r="G66" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="47" t="s">
+      <c r="H66" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I66" s="47" t="s">
+      <c r="I66" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="18" customHeight="1">
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C67" s="48">
+      <c r="C67" s="40">
         <v>167</v>
       </c>
       <c r="D67" s="9">
@@ -22841,7 +22830,7 @@
         <f>C67*0.86</f>
         <v>143.62</v>
       </c>
-      <c r="F67" s="49">
+      <c r="F67" s="41">
         <f>C67/G67</f>
         <v>89.304812834224592</v>
       </c>
@@ -22859,26 +22848,13 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="G65:I65"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="B13:I13"/>
@@ -22895,13 +22871,26 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="G28:I28"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -22929,69 +22918,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="23"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="23"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="24"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="23"/>
     </row>
     <row r="4" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B4" s="78"/>
-      <c r="C4" s="80" t="s">
+      <c r="B4" s="56"/>
+      <c r="C4" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="46" t="s">
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="80" t="s">
+      <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="81"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="24"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="19" t="s">
@@ -23000,28 +22989,28 @@
       <c r="D5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B6" s="21">
+      <c r="B6" s="17">
         <v>-35</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="41">
         <v>52.05590807065272</v>
       </c>
       <c r="D6" s="9">
@@ -23032,7 +23021,7 @@
         <f>C6*0.86</f>
         <v>44.768080940761337</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="41">
         <v>33.812192304106354</v>
       </c>
       <c r="G6" s="13">
@@ -23047,14 +23036,14 @@
         <f t="shared" ref="I6:I11" si="2">E6/F6</f>
         <v>1.3240218362097873</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="L6" s="26"/>
+      <c r="J6" s="24"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B7" s="21">
+      <c r="B7" s="17">
         <v>-30</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="41">
         <v>65.54594036268665</v>
       </c>
       <c r="D7" s="9">
@@ -23065,7 +23054,7 @@
         <f t="shared" ref="E7:E11" si="4">C7*0.86</f>
         <v>56.36950871191052</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="41">
         <v>39.504092289445367</v>
       </c>
       <c r="G7" s="13">
@@ -23080,14 +23069,14 @@
         <f t="shared" si="2"/>
         <v>1.4269283369148877</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="L7" s="26"/>
+      <c r="J7" s="24"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B8" s="21">
+      <c r="B8" s="17">
         <v>-25</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="41">
         <v>82.026479928287557</v>
       </c>
       <c r="D8" s="9">
@@ -23098,7 +23087,7 @@
         <f t="shared" si="4"/>
         <v>70.542772738327301</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="41">
         <v>45.358778640489753</v>
       </c>
       <c r="G8" s="13">
@@ -23113,14 +23102,14 @@
         <f t="shared" si="2"/>
         <v>1.5552176414943617</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="L8" s="26"/>
+      <c r="J8" s="24"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B9" s="21">
+      <c r="B9" s="17">
         <v>-20</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="41">
         <v>101.98967897412422</v>
       </c>
       <c r="D9" s="9">
@@ -23131,7 +23120,7 @@
         <f t="shared" si="4"/>
         <v>87.711123917746832</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="41">
         <v>51.215533927894789</v>
       </c>
       <c r="G9" s="13">
@@ -23146,14 +23135,14 @@
         <f t="shared" si="2"/>
         <v>1.7125882948176108</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="27"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="26"/>
     </row>
     <row r="10" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B10" s="21">
+      <c r="B10" s="17">
         <v>-15</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="41">
         <v>125.92768970686566</v>
       </c>
       <c r="D10" s="9">
@@ -23164,7 +23153,7 @@
         <f t="shared" si="4"/>
         <v>108.29781314790446</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="41">
         <v>56.913640722315776</v>
       </c>
       <c r="G10" s="13">
@@ -23179,14 +23168,14 @@
         <f t="shared" si="2"/>
         <v>1.9028445865253005</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="27"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B11" s="21">
+      <c r="B11" s="17">
         <v>-10</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="41">
         <v>154.33266433318059</v>
       </c>
       <c r="D11" s="9">
@@ -23197,7 +23186,7 @@
         <f t="shared" si="4"/>
         <v>132.72609132653531</v>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="41">
         <v>62.292381594407956</v>
       </c>
       <c r="G11" s="13">
@@ -23212,76 +23201,76 @@
         <f t="shared" si="2"/>
         <v>2.1306954065543424</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="27"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="26"/>
     </row>
     <row r="12" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B12" s="45"/>
+      <c r="B12" s="29"/>
     </row>
     <row r="13" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="23"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="23"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="22"/>
     </row>
     <row r="15" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="66"/>
-      <c r="E15" s="67"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59"/>
       <c r="F15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="65" t="s">
+      <c r="G15" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="66"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="24"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="2:12" ht="15.9" customHeight="1">
-      <c r="B16" s="78"/>
-      <c r="C16" s="80" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="46" t="s">
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="80" t="s">
+      <c r="G16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="24"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="19" t="s">
@@ -23290,28 +23279,28 @@
       <c r="D17" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="24"/>
+      <c r="J17" s="23"/>
     </row>
     <row r="18" spans="2:13" ht="15.9" customHeight="1">
       <c r="B18" s="18">
         <v>-35</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="41">
         <v>57.061329386066213</v>
       </c>
       <c r="D18" s="9">
@@ -23322,7 +23311,7 @@
         <f>C18*0.86</f>
         <v>49.072743272016943</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="41">
         <v>32.555151216040649</v>
       </c>
       <c r="G18" s="13">
@@ -23337,13 +23326,13 @@
         <f t="shared" ref="I18:I23" si="7">E18/F18</f>
         <v>1.5073726104469054</v>
       </c>
-      <c r="J18" s="25"/>
+      <c r="J18" s="24"/>
     </row>
     <row r="19" spans="2:13" ht="15.9" customHeight="1">
       <c r="B19" s="18">
         <v>-30</v>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="41">
         <v>70.553501169431968</v>
       </c>
       <c r="D19" s="9">
@@ -23354,7 +23343,7 @@
         <f t="shared" ref="E19:E23" si="9">C19*0.86</f>
         <v>60.676011005711494</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="41">
         <v>37.863858210940485</v>
       </c>
       <c r="G19" s="13">
@@ -23369,13 +23358,13 @@
         <f t="shared" si="7"/>
         <v>1.6024782965244573</v>
       </c>
-      <c r="J19" s="25"/>
+      <c r="J19" s="24"/>
     </row>
     <row r="20" spans="2:13" ht="15.9" customHeight="1">
       <c r="B20" s="18">
         <v>-25</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="41">
         <v>87.036673733431883</v>
       </c>
       <c r="D20" s="9">
@@ -23386,7 +23375,7 @@
         <f t="shared" si="9"/>
         <v>74.851539410751414</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="41">
         <v>43.253674205527837</v>
       </c>
       <c r="G20" s="13">
@@ -23401,13 +23390,13 @@
         <f t="shared" si="7"/>
         <v>1.7305244186905482</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="24"/>
     </row>
     <row r="21" spans="2:13" ht="15.9" customHeight="1">
       <c r="B21" s="18">
         <v>-20</v>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="41">
         <v>107.00299928473473</v>
       </c>
       <c r="D21" s="9">
@@ -23418,7 +23407,7 @@
         <f t="shared" si="9"/>
         <v>92.022579384871861</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="41">
         <v>48.563881770457989</v>
       </c>
       <c r="G21" s="13">
@@ -23433,13 +23422,13 @@
         <f t="shared" si="7"/>
         <v>1.8948769338461395</v>
       </c>
-      <c r="J21" s="25"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="2:13" ht="15.9" customHeight="1">
       <c r="B22" s="18">
         <v>-15</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="41">
         <v>130.94463003000948</v>
       </c>
       <c r="D22" s="9">
@@ -23450,7 +23439,7 @@
         <f t="shared" si="9"/>
         <v>112.61238182580814</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="41">
         <v>53.633763476386228</v>
       </c>
       <c r="G22" s="13">
@@ -23465,13 +23454,13 @@
         <f t="shared" si="7"/>
         <v>2.0996546676309396</v>
       </c>
-      <c r="J22" s="25"/>
+      <c r="J22" s="24"/>
     </row>
     <row r="23" spans="2:13" ht="15.9" customHeight="1">
       <c r="B23" s="18">
         <v>-10</v>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="41">
         <v>159.35371817592491</v>
       </c>
       <c r="D23" s="9">
@@ -23482,7 +23471,7 @@
         <f t="shared" si="9"/>
         <v>137.04419763129542</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="41">
         <v>58.302601893967818</v>
       </c>
       <c r="G23" s="13">
@@ -23497,78 +23486,78 @@
         <f t="shared" si="7"/>
         <v>2.3505674391776066</v>
       </c>
-      <c r="J23" s="25"/>
+      <c r="J23" s="24"/>
     </row>
     <row r="24" spans="2:13" ht="15.9" customHeight="1">
       <c r="B24" s="15"/>
     </row>
     <row r="25" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B25" s="72" t="s">
+      <c r="B25" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="23"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="22"/>
       <c r="M25" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="23"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="67"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="59"/>
       <c r="F27" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="65" t="s">
+      <c r="G27" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="66"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="24"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B28" s="78"/>
-      <c r="C28" s="80" t="s">
+      <c r="B28" s="56"/>
+      <c r="C28" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="81"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="46" t="s">
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="80" t="s">
+      <c r="G28" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H28" s="81"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="24"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="19" t="s">
@@ -23577,28 +23566,28 @@
       <c r="D29" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="24"/>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B30" s="22">
+      <c r="B30" s="21">
         <v>-35</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="41">
         <v>62.06566828494023</v>
       </c>
       <c r="D30" s="9">
@@ -23609,7 +23598,7 @@
         <f>C30*0.86</f>
         <v>53.376474725048595</v>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="41">
         <v>31.236331176704478</v>
       </c>
       <c r="G30" s="13">
@@ -23624,13 +23613,13 @@
         <f t="shared" ref="I30:I35" si="12">E30/F30</f>
         <v>1.7087946219771115</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B31" s="22">
+      <c r="B31" s="21">
         <v>-30</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="41">
         <v>75.559573538323889</v>
       </c>
       <c r="D31" s="9">
@@ -23641,7 +23630,7 @@
         <f t="shared" ref="E31:E35" si="14">C31*0.86</f>
         <v>64.981233242958538</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="41">
         <v>36.139877368386351</v>
       </c>
       <c r="G31" s="13">
@@ -23656,14 +23645,14 @@
         <f t="shared" si="12"/>
         <v>1.798047972896593</v>
       </c>
-      <c r="J31" s="25"/>
-      <c r="K31" s="27"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="26"/>
     </row>
     <row r="32" spans="2:13" ht="15.9" customHeight="1">
-      <c r="B32" s="22">
+      <c r="B32" s="21">
         <v>-25</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="41">
         <v>92.044973079408862</v>
       </c>
       <c r="D32" s="9">
@@ -23674,7 +23663,7 @@
         <f t="shared" si="14"/>
         <v>79.15867684829162</v>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="41">
         <v>41.0428551937379</v>
       </c>
       <c r="G32" s="13">
@@ -23689,14 +23678,14 @@
         <f t="shared" si="12"/>
         <v>1.9286834815617124</v>
       </c>
-      <c r="J32" s="25"/>
-      <c r="K32" s="27"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="26"/>
     </row>
     <row r="33" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B33" s="22">
+      <c r="B33" s="21">
         <v>-20</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="41">
         <v>112.01401911486397</v>
       </c>
       <c r="D33" s="9">
@@ -23707,7 +23696,7 @@
         <f t="shared" si="14"/>
         <v>96.332056438783013</v>
       </c>
-      <c r="F33" s="49">
+      <c r="F33" s="41">
         <v>45.784547223414386</v>
       </c>
       <c r="G33" s="13">
@@ -23722,14 +23711,14 @@
         <f t="shared" si="12"/>
         <v>2.1040299026811922</v>
       </c>
-      <c r="J33" s="25"/>
-      <c r="K33" s="27"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="26"/>
     </row>
     <row r="34" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B34" s="22">
+      <c r="B34" s="21">
         <v>-15</v>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="41">
         <v>135.95886385135813</v>
       </c>
       <c r="D34" s="9">
@@ -23740,7 +23729,7 @@
         <f t="shared" si="14"/>
         <v>116.92462291216799</v>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="41">
         <v>50.204236028071115</v>
       </c>
       <c r="G34" s="13">
@@ -23755,13 +23744,13 @@
         <f t="shared" si="12"/>
         <v>2.3289792288999469</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="24"/>
     </row>
     <row r="35" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B35" s="22">
+      <c r="B35" s="21">
         <v>-10</v>
       </c>
-      <c r="C35" s="49">
+      <c r="C35" s="41">
         <v>164.37165949556018</v>
       </c>
       <c r="D35" s="9">
@@ -23772,7 +23761,7 @@
         <f t="shared" si="14"/>
         <v>141.35962716618175</v>
       </c>
-      <c r="F35" s="49">
+      <c r="F35" s="41">
         <v>54.141204178363346</v>
       </c>
       <c r="G35" s="13">
@@ -23787,75 +23776,75 @@
         <f t="shared" si="12"/>
         <v>2.61094353757787</v>
       </c>
-      <c r="J35" s="25"/>
+      <c r="J35" s="24"/>
     </row>
     <row r="36" spans="2:11" ht="15.9" customHeight="1">
       <c r="B36" s="15"/>
     </row>
     <row r="37" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B37" s="72" t="s">
+      <c r="B37" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="23"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="23"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="39" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="66"/>
-      <c r="E39" s="67"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="65" t="s">
+      <c r="G39" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="66"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="24"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="23"/>
     </row>
     <row r="40" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B40" s="78"/>
-      <c r="C40" s="80" t="s">
+      <c r="B40" s="56"/>
+      <c r="C40" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="46" t="s">
+      <c r="D40" s="61"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="80" t="s">
+      <c r="G40" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="81"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="24"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C41" s="10" t="s">
@@ -23879,13 +23868,13 @@
       <c r="I41" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="24"/>
+      <c r="J41" s="23"/>
     </row>
     <row r="42" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B42" s="21">
+      <c r="B42" s="17">
         <v>-35</v>
       </c>
-      <c r="C42" s="49">
+      <c r="C42" s="41">
         <v>67.068924767274709</v>
       </c>
       <c r="D42" s="9">
@@ -23896,7 +23885,7 @@
         <f>C42*0.86</f>
         <v>57.679275299856251</v>
       </c>
-      <c r="F42" s="49">
+      <c r="F42" s="41">
         <v>29.852261172288159</v>
       </c>
       <c r="G42" s="13">
@@ -23911,13 +23900,13 @@
         <f t="shared" ref="I42:I47" si="17">E42/F42</f>
         <v>1.9321576669508673</v>
       </c>
-      <c r="J42" s="25"/>
+      <c r="J42" s="24"/>
     </row>
     <row r="43" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B43" s="21">
+      <c r="B43" s="17">
         <v>-30</v>
       </c>
-      <c r="C43" s="49">
+      <c r="C43" s="41">
         <v>80.564157469362385</v>
       </c>
       <c r="D43" s="9">
@@ -23928,7 +23917,7 @@
         <f t="shared" ref="E43:E47" si="19">C43*0.86</f>
         <v>69.285175423651651</v>
       </c>
-      <c r="F43" s="49">
+      <c r="F43" s="41">
         <v>34.328678747973299</v>
       </c>
       <c r="G43" s="13">
@@ -23943,13 +23932,13 @@
         <f t="shared" si="17"/>
         <v>2.0182884384311506</v>
       </c>
-      <c r="J43" s="25"/>
+      <c r="J43" s="24"/>
     </row>
     <row r="44" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B44" s="21">
+      <c r="B44" s="17">
         <v>-25</v>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="41">
         <v>97.051377966218524</v>
       </c>
       <c r="D44" s="9">
@@ -23960,7 +23949,7 @@
         <f t="shared" si="19"/>
         <v>83.464185050947933</v>
       </c>
-      <c r="F44" s="49">
+      <c r="F44" s="41">
         <v>38.722850591310277</v>
       </c>
       <c r="G44" s="13">
@@ -23975,13 +23964,13 @@
         <f t="shared" si="17"/>
         <v>2.1554246078587505</v>
       </c>
-      <c r="J44" s="25"/>
+      <c r="J44" s="24"/>
     </row>
     <row r="45" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B45" s="21">
+      <c r="B45" s="17">
         <v>-20</v>
       </c>
-      <c r="C45" s="49">
+      <c r="C45" s="41">
         <v>117.02273846451197</v>
       </c>
       <c r="D45" s="9">
@@ -23992,7 +23981,7 @@
         <f t="shared" si="19"/>
         <v>100.6395550794803</v>
       </c>
-      <c r="F45" s="49">
+      <c r="F45" s="41">
         <v>42.874059272954334</v>
       </c>
       <c r="G45" s="13">
@@ -24007,13 +23996,13 @@
         <f t="shared" si="17"/>
         <v>2.3473297557100081</v>
       </c>
-      <c r="J45" s="25"/>
+      <c r="J45" s="24"/>
     </row>
     <row r="46" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B46" s="21">
+      <c r="B46" s="17">
         <v>-15</v>
       </c>
-      <c r="C46" s="49">
+      <c r="C46" s="41">
         <v>140.97039117091168</v>
       </c>
       <c r="D46" s="9">
@@ -24024,7 +24013,7 @@
         <f t="shared" si="19"/>
         <v>121.23453640698405</v>
       </c>
-      <c r="F46" s="49">
+      <c r="F46" s="41">
         <v>46.621587363560757</v>
       </c>
       <c r="G46" s="13">
@@ -24039,13 +24028,13 @@
         <f t="shared" si="17"/>
         <v>2.6003948656141311</v>
       </c>
-      <c r="J46" s="25"/>
+      <c r="J46" s="24"/>
     </row>
     <row r="47" spans="2:11" ht="15.9" customHeight="1">
-      <c r="B47" s="21">
+      <c r="B47" s="17">
         <v>-10</v>
       </c>
-      <c r="C47" s="49">
+      <c r="C47" s="41">
         <v>169.38648829208643</v>
       </c>
       <c r="D47" s="9">
@@ -24056,7 +24045,7 @@
         <f t="shared" si="19"/>
         <v>145.67237993119431</v>
       </c>
-      <c r="F47" s="49">
+      <c r="F47" s="41">
         <v>49.804717433784859</v>
       </c>
       <c r="G47" s="13">
@@ -24071,75 +24060,75 @@
         <f t="shared" si="17"/>
         <v>2.9248711254082522</v>
       </c>
-      <c r="J47" s="25"/>
+      <c r="J47" s="24"/>
     </row>
     <row r="48" spans="2:11" ht="18" customHeight="1">
       <c r="B48" s="15"/>
     </row>
     <row r="49" spans="2:11" ht="18" customHeight="1">
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="23"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="22"/>
     </row>
     <row r="50" spans="2:11" ht="18" customHeight="1">
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="69"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="23"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="22"/>
     </row>
     <row r="51" spans="2:11" ht="18" customHeight="1">
-      <c r="B51" s="77" t="s">
+      <c r="B51" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="C51" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="66"/>
-      <c r="E51" s="67"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="59"/>
       <c r="F51" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G51" s="65" t="s">
+      <c r="G51" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H51" s="66"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="24"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="23"/>
     </row>
     <row r="52" spans="2:11" ht="18" customHeight="1">
-      <c r="B52" s="78"/>
-      <c r="C52" s="80" t="s">
+      <c r="B52" s="56"/>
+      <c r="C52" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="46" t="s">
+      <c r="D52" s="61"/>
+      <c r="E52" s="62"/>
+      <c r="F52" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="80" t="s">
+      <c r="G52" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H52" s="81"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="24"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="62"/>
+      <c r="J52" s="23"/>
     </row>
     <row r="53" spans="2:11" ht="18" customHeight="1">
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C53" s="19" t="s">
@@ -24148,28 +24137,28 @@
       <c r="D53" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E53" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="21" t="s">
+      <c r="G53" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I53" s="21" t="s">
+      <c r="I53" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J53" s="24"/>
+      <c r="J53" s="23"/>
     </row>
     <row r="54" spans="2:11" ht="18" customHeight="1">
       <c r="B54" s="17">
         <v>-35</v>
       </c>
-      <c r="C54" s="49">
+      <c r="C54" s="41">
         <v>72.071098833069698</v>
       </c>
       <c r="D54" s="9">
@@ -24180,7 +24169,7 @@
         <f>C54*0.86</f>
         <v>61.981144996439937</v>
       </c>
-      <c r="F54" s="49">
+      <c r="F54" s="41">
         <v>28.399470188982054</v>
       </c>
       <c r="G54" s="13">
@@ -24195,13 +24184,13 @@
         <f t="shared" ref="I54:I59" si="22">E54/F54</f>
         <v>2.1824753977447906</v>
       </c>
-      <c r="J54" s="25"/>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="2:11" ht="18" customHeight="1">
       <c r="B55" s="17">
         <v>-30</v>
       </c>
-      <c r="C55" s="49">
+      <c r="C55" s="41">
         <v>85.567252962547457</v>
       </c>
       <c r="D55" s="9">
@@ -24212,7 +24201,7 @@
         <f t="shared" ref="E55:E59" si="24">C55*0.86</f>
         <v>73.587837547790812</v>
       </c>
-      <c r="F55" s="49">
+      <c r="F55" s="41">
         <v>32.426791335891686</v>
       </c>
       <c r="G55" s="13">
@@ -24227,14 +24216,14 @@
         <f t="shared" si="22"/>
         <v>2.2693530416109935</v>
       </c>
-      <c r="J55" s="25"/>
-      <c r="K55" s="27"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="26"/>
     </row>
     <row r="56" spans="2:11" ht="18" customHeight="1">
       <c r="B56" s="17">
         <v>-25</v>
       </c>
-      <c r="C56" s="49">
+      <c r="C56" s="41">
         <v>102.05588839386084</v>
       </c>
       <c r="D56" s="9">
@@ -24245,7 +24234,7 @@
         <f t="shared" si="24"/>
         <v>87.768064018720324</v>
       </c>
-      <c r="F56" s="49">
+      <c r="F56" s="41">
         <v>36.29018938443533</v>
       </c>
       <c r="G56" s="13">
@@ -24260,13 +24249,13 @@
         <f t="shared" si="22"/>
         <v>2.4185066407055893</v>
       </c>
-      <c r="J56" s="25"/>
+      <c r="J56" s="24"/>
     </row>
     <row r="57" spans="2:11" ht="18" customHeight="1">
       <c r="B57" s="17">
         <v>-20</v>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="41">
         <v>122.02915733367874</v>
       </c>
       <c r="D57" s="9">
@@ -24277,7 +24266,7 @@
         <f t="shared" si="24"/>
         <v>104.94507530696372</v>
       </c>
-      <c r="F57" s="49">
+      <c r="F57" s="41">
         <v>39.828946905268161</v>
       </c>
       <c r="G57" s="13">
@@ -24292,13 +24281,13 @@
         <f t="shared" si="22"/>
         <v>2.6348945543695175</v>
       </c>
-      <c r="J57" s="25"/>
+      <c r="J57" s="24"/>
     </row>
     <row r="58" spans="2:11" ht="18" customHeight="1">
       <c r="B58" s="17">
         <v>-15</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="41">
         <v>145.97921198867004</v>
       </c>
       <c r="D58" s="9">
@@ -24309,7 +24298,7 @@
         <f t="shared" si="24"/>
         <v>125.54212231025623</v>
       </c>
-      <c r="F58" s="49">
+      <c r="F58" s="41">
         <v>42.882346469045537</v>
       </c>
       <c r="G58" s="13">
@@ -24324,13 +24313,13 @@
         <f t="shared" si="22"/>
         <v>2.9275945149335136</v>
       </c>
-      <c r="J58" s="25"/>
+      <c r="J58" s="24"/>
     </row>
     <row r="59" spans="2:11" ht="18" customHeight="1">
       <c r="B59" s="17">
         <v>-10</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="41">
         <v>174.39820456550356</v>
       </c>
       <c r="D59" s="9">
@@ -24341,7 +24330,7 @@
         <f t="shared" si="24"/>
         <v>149.98245592633307</v>
       </c>
-      <c r="F59" s="49">
+      <c r="F59" s="41">
         <v>45.289670646422721</v>
       </c>
       <c r="G59" s="13">
@@ -24356,68 +24345,68 @@
         <f t="shared" si="22"/>
         <v>3.3116261122154946</v>
       </c>
-      <c r="J59" s="25"/>
+      <c r="J59" s="24"/>
     </row>
     <row r="62" spans="2:11" ht="18" customHeight="1">
-      <c r="B62" s="72" t="s">
+      <c r="B62" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
     </row>
     <row r="63" spans="2:11" ht="18" customHeight="1">
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="71"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="54"/>
     </row>
     <row r="64" spans="2:11" ht="18" customHeight="1">
-      <c r="B64" s="77" t="s">
+      <c r="B64" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="65" t="s">
+      <c r="C64" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="66"/>
-      <c r="E64" s="67"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="59"/>
       <c r="F64" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="65" t="s">
+      <c r="G64" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H64" s="66"/>
-      <c r="I64" s="67"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="59"/>
     </row>
     <row r="65" spans="2:9" ht="18" customHeight="1">
-      <c r="B65" s="78"/>
-      <c r="C65" s="80" t="s">
+      <c r="B65" s="56"/>
+      <c r="C65" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D65" s="81"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="46" t="s">
+      <c r="D65" s="61"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G65" s="80" t="s">
+      <c r="G65" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H65" s="81"/>
-      <c r="I65" s="82"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="62"/>
     </row>
     <row r="66" spans="2:9" ht="18" customHeight="1">
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C66" s="10" t="s">
@@ -24426,27 +24415,27 @@
       <c r="D66" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="47" t="s">
+      <c r="E66" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G66" s="47" t="s">
+      <c r="G66" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="47" t="s">
+      <c r="H66" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I66" s="47" t="s">
+      <c r="I66" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="18" customHeight="1">
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C67" s="48">
+      <c r="C67" s="40">
         <v>89</v>
       </c>
       <c r="D67" s="9">
@@ -24457,7 +24446,7 @@
         <f>C67*0.86</f>
         <v>76.539999999999992</v>
       </c>
-      <c r="F67" s="49">
+      <c r="F67" s="41">
         <f>C67/G67</f>
         <v>46.354166666666671</v>
       </c>
@@ -24475,11 +24464,27 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="B13:I13"/>
@@ -24496,27 +24501,11 @@
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C40:E40"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24532,9 +24521,9 @@
   <cols>
     <col min="1" max="1" width="1.109375" style="8" customWidth="1"/>
     <col min="2" max="2" width="12.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="8" style="55" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="55" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" style="55" customWidth="1"/>
+    <col min="3" max="3" width="8" style="46" customWidth="1"/>
+    <col min="4" max="5" width="8.6640625" style="46" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" style="46" customWidth="1"/>
     <col min="7" max="9" width="9.6640625" style="8" customWidth="1"/>
     <col min="10" max="10" width="1.33203125" style="8" customWidth="1"/>
     <col min="11" max="19" width="9" style="8"/>
@@ -24543,69 +24532,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.6">
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="23"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="2:12" ht="15.75" customHeight="1">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="23"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="2:12" ht="15.6">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="24"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="23"/>
     </row>
     <row r="4" spans="2:12" ht="15.6">
-      <c r="B4" s="78"/>
-      <c r="C4" s="80" t="s">
+      <c r="B4" s="56"/>
+      <c r="C4" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="57" t="s">
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="80" t="s">
+      <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="81"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="24"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="31.2">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -24620,55 +24609,55 @@
       <c r="F5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="2:12" ht="15.6">
-      <c r="B6" s="58">
+      <c r="B6" s="21">
         <v>-35</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="85">
         <v>41.998037989741533</v>
       </c>
       <c r="D6" s="19">
         <f>C6*3.41</f>
         <v>143.21330954501863</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="86">
         <f>C6*0.86</f>
         <v>36.118312671177719</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="85">
         <v>27.353683661748953</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="45">
         <f t="shared" ref="G6:G11" si="0">C6/F6</f>
         <v>1.5353704645078958</v>
       </c>
-      <c r="H6" s="54">
+      <c r="H6" s="45">
         <f t="shared" ref="H6:H11" si="1">D6/F6</f>
         <v>5.2356132839719249</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="45">
         <f t="shared" ref="I6:I11" si="2">E6/F6</f>
         <v>1.3204185994767905</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="L6" s="26"/>
+      <c r="J6" s="24"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="15.6">
-      <c r="B7" s="58">
+      <c r="B7" s="21">
         <v>-30</v>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="42">
         <v>52.91132254060043</v>
       </c>
       <c r="D7" s="19">
@@ -24679,62 +24668,62 @@
         <f t="shared" ref="E7:E11" si="4">C7*0.86</f>
         <v>45.50373738491637</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="42">
         <v>31.958366795955794</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="45">
         <f t="shared" si="0"/>
         <v>1.6556328700531766</v>
       </c>
-      <c r="H7" s="54">
+      <c r="H7" s="45">
         <f t="shared" si="1"/>
         <v>5.6457080868813323</v>
       </c>
-      <c r="I7" s="54">
+      <c r="I7" s="45">
         <f t="shared" si="2"/>
         <v>1.4238442682457317</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="L7" s="26"/>
+      <c r="J7" s="24"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="2:12" ht="15.6">
-      <c r="B8" s="58">
+      <c r="B8" s="21">
         <v>-25</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="85">
         <v>66.243893874569721</v>
       </c>
       <c r="D8" s="19">
         <f t="shared" si="3"/>
         <v>225.89167811228276</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="86">
         <f t="shared" si="4"/>
         <v>56.969748732129958</v>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="85">
         <v>36.694742270957995</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="45">
         <f t="shared" si="0"/>
         <v>1.8052693594471261</v>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="45">
         <f t="shared" si="1"/>
         <v>6.1559685157146999</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="45">
         <f t="shared" si="2"/>
         <v>1.5525316491245285</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="L8" s="26"/>
+      <c r="J8" s="24"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="15.6">
-      <c r="B9" s="58">
+      <c r="B9" s="21">
         <v>-20</v>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="42">
         <v>82.393897597044315</v>
       </c>
       <c r="D9" s="19">
@@ -24745,62 +24734,62 @@
         <f t="shared" si="4"/>
         <v>70.858751933458109</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="42">
         <v>41.432791492229484</v>
       </c>
-      <c r="G9" s="54">
+      <c r="G9" s="45">
         <f t="shared" si="0"/>
         <v>1.9886156502995191</v>
       </c>
-      <c r="H9" s="54">
+      <c r="H9" s="45">
         <f t="shared" si="1"/>
         <v>6.7811793675213599</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="45">
         <f t="shared" si="2"/>
         <v>1.7102094592575863</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="27"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="26"/>
     </row>
     <row r="10" spans="2:12" ht="15.6">
-      <c r="B10" s="58">
+      <c r="B10" s="21">
         <v>-15</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="85">
         <v>101.7594793134194</v>
       </c>
       <c r="D10" s="19">
         <f t="shared" si="3"/>
         <v>346.9998244587602</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="86">
         <f t="shared" si="4"/>
         <v>87.513152209540692</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="85">
         <v>46.042495865244213</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="45">
         <f t="shared" si="0"/>
         <v>2.2101208329636597</v>
       </c>
-      <c r="H10" s="54">
+      <c r="H10" s="45">
         <f t="shared" si="1"/>
         <v>7.5365120404060804</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="45">
         <f t="shared" si="2"/>
         <v>1.9007039163487476</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="27"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" spans="2:12" ht="15.6">
-      <c r="B11" s="58">
+      <c r="B11" s="21">
         <v>-10</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="42">
         <v>124.73878462908991</v>
       </c>
       <c r="D11" s="19">
@@ -24811,91 +24800,91 @@
         <f t="shared" si="4"/>
         <v>107.27535478101731</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="42">
         <v>50.393836795476091</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="45">
         <f t="shared" si="0"/>
         <v>2.4752785769288326</v>
       </c>
-      <c r="H11" s="54">
+      <c r="H11" s="45">
         <f t="shared" si="1"/>
         <v>8.4406999473273192</v>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="45">
         <f t="shared" si="2"/>
         <v>2.1287395761587962</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="27"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="26"/>
     </row>
     <row r="12" spans="2:12" ht="15.6">
-      <c r="B12" s="45"/>
+      <c r="B12" s="29"/>
     </row>
     <row r="13" spans="2:12" ht="15.6">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="23"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="2:12" ht="15.75" customHeight="1">
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="23"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="22"/>
     </row>
     <row r="15" spans="2:12" ht="15.6">
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="66"/>
-      <c r="E15" s="67"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59"/>
       <c r="F15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="65" t="s">
+      <c r="G15" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="66"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="24"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="2:12" ht="15.6">
-      <c r="B16" s="78"/>
-      <c r="C16" s="80" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="57" t="s">
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="80" t="s">
+      <c r="G16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="24"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="2:13" ht="31.2">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="14" t="s">
@@ -24910,22 +24899,22 @@
       <c r="F17" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="24"/>
+      <c r="J17" s="23"/>
     </row>
     <row r="18" spans="2:13" ht="15.6">
       <c r="B18" s="18">
         <v>-35</v>
       </c>
-      <c r="C18" s="50">
+      <c r="C18" s="42">
         <v>47.002423772997389</v>
       </c>
       <c r="D18" s="19">
@@ -24936,28 +24925,28 @@
         <f>C18*0.86</f>
         <v>40.422084444777752</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="42">
         <v>26.336751545560968</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="45">
         <f t="shared" ref="G18:G23" si="5">C18/F18</f>
         <v>1.7846705084978332</v>
       </c>
-      <c r="H18" s="54">
+      <c r="H18" s="45">
         <f t="shared" ref="H18:H23" si="6">D18/F18</f>
         <v>6.0857264339776114</v>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="45">
         <f t="shared" ref="I18:I23" si="7">E18/F18</f>
         <v>1.5348166373081364</v>
       </c>
-      <c r="J18" s="25"/>
+      <c r="J18" s="24"/>
     </row>
     <row r="19" spans="2:13" ht="15.6">
       <c r="B19" s="18">
         <v>-30</v>
       </c>
-      <c r="C19" s="50">
+      <c r="C19" s="42">
         <v>57.917439148304524</v>
       </c>
       <c r="D19" s="19">
@@ -24968,28 +24957,28 @@
         <f t="shared" ref="E19:E23" si="9">C19*0.86</f>
         <v>49.808997667541888</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="42">
         <v>30.631435856041733</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="45">
         <f t="shared" si="5"/>
         <v>1.8907843373878574</v>
       </c>
-      <c r="H19" s="54">
+      <c r="H19" s="45">
         <f t="shared" si="6"/>
         <v>6.4475745904925938</v>
       </c>
-      <c r="I19" s="54">
+      <c r="I19" s="45">
         <f t="shared" si="7"/>
         <v>1.6260745301535573</v>
       </c>
-      <c r="J19" s="25"/>
+      <c r="J19" s="24"/>
     </row>
     <row r="20" spans="2:13" ht="15.6">
       <c r="B20" s="18">
         <v>-25</v>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="42">
         <v>71.252140548394323</v>
       </c>
       <c r="D20" s="19">
@@ -25000,28 +24989,28 @@
         <f t="shared" si="9"/>
         <v>61.276840871619115</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="42">
         <v>34.99173643593263</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="45">
         <f t="shared" si="5"/>
         <v>2.0362562080579196</v>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="45">
         <f t="shared" si="6"/>
         <v>6.9436336694775065</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="45">
         <f t="shared" si="7"/>
         <v>1.7511803389298108</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="24"/>
     </row>
     <row r="21" spans="2:13" ht="15.6">
       <c r="B21" s="18">
         <v>-20</v>
       </c>
-      <c r="C21" s="50">
+      <c r="C21" s="42">
         <v>87.4046735786618</v>
       </c>
       <c r="D21" s="19">
@@ -25032,28 +25021,28 @@
         <f t="shared" si="9"/>
         <v>75.168019277649151</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="42">
         <v>39.287634690707577</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="45">
         <f t="shared" si="5"/>
         <v>2.2247374846247743</v>
       </c>
-      <c r="H21" s="54">
+      <c r="H21" s="45">
         <f t="shared" si="6"/>
         <v>7.5863548225704811</v>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="45">
         <f t="shared" si="7"/>
         <v>1.9132742367773061</v>
       </c>
-      <c r="J21" s="25"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="2:13" ht="15.6">
       <c r="B22" s="18">
         <v>-15</v>
       </c>
-      <c r="C22" s="50">
+      <c r="C22" s="42">
         <v>106.77318384450206</v>
       </c>
       <c r="D22" s="19">
@@ -25064,28 +25053,28 @@
         <f t="shared" si="9"/>
         <v>91.824938106271773</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="42">
         <v>43.389112025840539</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="45">
         <f t="shared" si="5"/>
         <v>2.4608289697404482</v>
       </c>
-      <c r="H22" s="54">
+      <c r="H22" s="45">
         <f t="shared" si="6"/>
         <v>8.3914267868149288</v>
       </c>
-      <c r="I22" s="54">
+      <c r="I22" s="45">
         <f t="shared" si="7"/>
         <v>2.1163129139767856</v>
       </c>
-      <c r="J22" s="25"/>
+      <c r="J22" s="24"/>
     </row>
     <row r="23" spans="2:13" ht="15.6">
       <c r="B23" s="18">
         <v>-10</v>
       </c>
-      <c r="C23" s="50">
+      <c r="C23" s="42">
         <v>129.75581695131004</v>
       </c>
       <c r="D23" s="19">
@@ -25096,93 +25085,93 @@
         <f t="shared" si="9"/>
         <v>111.59000257812663</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F23" s="42">
         <v>47.166149846805418</v>
       </c>
-      <c r="G23" s="54">
+      <c r="G23" s="45">
         <f t="shared" si="5"/>
         <v>2.7510368637837512</v>
       </c>
-      <c r="H23" s="54">
+      <c r="H23" s="45">
         <f t="shared" si="6"/>
         <v>9.3810357055025921</v>
       </c>
-      <c r="I23" s="54">
+      <c r="I23" s="45">
         <f t="shared" si="7"/>
         <v>2.3658917028540261</v>
       </c>
-      <c r="J23" s="25"/>
+      <c r="J23" s="24"/>
     </row>
     <row r="24" spans="2:13" ht="15.6">
       <c r="B24" s="15"/>
     </row>
     <row r="25" spans="2:13" ht="15.6">
-      <c r="B25" s="72" t="s">
+      <c r="B25" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="23"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="22"/>
       <c r="M25" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="15.75" customHeight="1">
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="23"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="2:13" ht="15.6">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="67"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="59"/>
       <c r="F27" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="65" t="s">
+      <c r="G27" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="66"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="24"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" spans="2:13" ht="15.6">
-      <c r="B28" s="78"/>
-      <c r="C28" s="80" t="s">
+      <c r="B28" s="56"/>
+      <c r="C28" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="81"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="57" t="s">
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="80" t="s">
+      <c r="G28" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H28" s="81"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="24"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="2:13" ht="31.2">
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="14" t="s">
@@ -25197,54 +25186,54 @@
       <c r="F29" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="24"/>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="2:13" ht="15.6">
-      <c r="B30" s="22">
+      <c r="B30" s="21">
         <v>-35</v>
       </c>
-      <c r="C30" s="50">
+      <c r="C30" s="85">
         <v>52.005933893434793</v>
       </c>
       <c r="D30" s="19">
         <f>C30*3.41</f>
         <v>177.34023457661266</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="86">
         <f>C30*0.86</f>
         <v>44.725103148353924</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="85">
         <v>25.269840951940697</v>
       </c>
-      <c r="G30" s="54">
+      <c r="G30" s="45">
         <f t="shared" ref="G30:G35" si="10">C30/F30</f>
         <v>2.0580237917738375</v>
       </c>
-      <c r="H30" s="54">
+      <c r="H30" s="45">
         <f t="shared" ref="H30:H35" si="11">D30/F30</f>
         <v>7.0178611299487867</v>
       </c>
-      <c r="I30" s="54">
+      <c r="I30" s="45">
         <f t="shared" ref="I30:I35" si="12">E30/F30</f>
         <v>1.7699004609255002</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="2:13" ht="15.6">
-      <c r="B31" s="22">
+      <c r="B31" s="21">
         <v>-30</v>
       </c>
-      <c r="C31" s="50">
+      <c r="C31" s="42">
         <v>62.922351626509219</v>
       </c>
       <c r="D31" s="19">
@@ -25255,62 +25244,62 @@
         <f t="shared" ref="E31:E35" si="14">C31*0.86</f>
         <v>54.11322239879793</v>
       </c>
-      <c r="F31" s="50">
+      <c r="F31" s="42">
         <v>29.236754724986707</v>
       </c>
-      <c r="G31" s="54">
+      <c r="G31" s="45">
         <f t="shared" si="10"/>
         <v>2.1521660737788273</v>
       </c>
-      <c r="H31" s="54">
+      <c r="H31" s="45">
         <f t="shared" si="11"/>
         <v>7.3388863115858012</v>
       </c>
-      <c r="I31" s="54">
+      <c r="I31" s="45">
         <f t="shared" si="12"/>
         <v>1.8508628234497915</v>
       </c>
-      <c r="J31" s="25"/>
-      <c r="K31" s="27"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="26"/>
     </row>
     <row r="32" spans="2:13" ht="15.6">
-      <c r="B32" s="22">
+      <c r="B32" s="21">
         <v>-25</v>
       </c>
-      <c r="C32" s="50">
+      <c r="C32" s="85">
         <v>76.258854626038641</v>
       </c>
       <c r="D32" s="19">
         <f t="shared" si="13"/>
         <v>260.04269427479176</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="86">
         <f t="shared" si="14"/>
         <v>65.582614978393224</v>
       </c>
-      <c r="F32" s="50">
+      <c r="F32" s="85">
         <v>33.203208696057622</v>
       </c>
-      <c r="G32" s="54">
+      <c r="G32" s="45">
         <f t="shared" si="10"/>
         <v>2.296731479301072</v>
       </c>
-      <c r="H32" s="54">
+      <c r="H32" s="45">
         <f t="shared" si="11"/>
         <v>7.8318543444166551</v>
       </c>
-      <c r="I32" s="54">
+      <c r="I32" s="45">
         <f t="shared" si="12"/>
         <v>1.9751890721989216</v>
       </c>
-      <c r="J32" s="25"/>
-      <c r="K32" s="27"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="26"/>
     </row>
     <row r="33" spans="2:11" ht="15.6">
-      <c r="B33" s="22">
+      <c r="B33" s="21">
         <v>-20</v>
       </c>
-      <c r="C33" s="50">
+      <c r="C33" s="42">
         <v>92.413588497418061</v>
       </c>
       <c r="D33" s="19">
@@ -25321,61 +25310,61 @@
         <f t="shared" si="14"/>
         <v>79.475686107779538</v>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="42">
         <v>37.039184270627359</v>
       </c>
-      <c r="G33" s="54">
+      <c r="G33" s="45">
         <f t="shared" si="10"/>
         <v>2.4950222397501194</v>
       </c>
-      <c r="H33" s="54">
+      <c r="H33" s="45">
         <f t="shared" si="11"/>
         <v>8.5080258375479065</v>
       </c>
-      <c r="I33" s="54">
+      <c r="I33" s="45">
         <f t="shared" si="12"/>
         <v>2.1457191261851025</v>
       </c>
-      <c r="J33" s="25"/>
-      <c r="K33" s="27"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="26"/>
     </row>
     <row r="34" spans="2:11" ht="15.6">
-      <c r="B34" s="22">
+      <c r="B34" s="21">
         <v>-15</v>
       </c>
-      <c r="C34" s="50">
+      <c r="C34" s="85">
         <v>111.78469884604255</v>
       </c>
       <c r="D34" s="19">
         <f t="shared" si="13"/>
         <v>381.18582306500508</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="86">
         <f t="shared" si="14"/>
         <v>96.134841007596592</v>
       </c>
-      <c r="F34" s="50">
+      <c r="F34" s="85">
         <v>40.614662854169886</v>
       </c>
-      <c r="G34" s="54">
+      <c r="G34" s="45">
         <f t="shared" si="10"/>
         <v>2.752323692736641</v>
       </c>
-      <c r="H34" s="54">
+      <c r="H34" s="45">
         <f t="shared" si="11"/>
         <v>9.3854237922319452</v>
       </c>
-      <c r="I34" s="54">
+      <c r="I34" s="45">
         <f t="shared" si="12"/>
         <v>2.3669983757535111</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="24"/>
     </row>
     <row r="35" spans="2:11" ht="15.6">
-      <c r="B35" s="22">
+      <c r="B35" s="21">
         <v>-10</v>
       </c>
-      <c r="C35" s="50">
+      <c r="C35" s="42">
         <v>134.77033127730712</v>
       </c>
       <c r="D35" s="19">
@@ -25386,120 +25375,120 @@
         <f t="shared" si="14"/>
         <v>115.90248489848412</v>
       </c>
-      <c r="F35" s="50">
+      <c r="F35" s="42">
         <v>43.799625852159103</v>
       </c>
-      <c r="G35" s="54">
+      <c r="G35" s="45">
         <f t="shared" si="10"/>
         <v>3.0769744867732385</v>
       </c>
-      <c r="H35" s="54">
+      <c r="H35" s="45">
         <f t="shared" si="11"/>
         <v>10.492482999896744</v>
       </c>
-      <c r="I35" s="54">
+      <c r="I35" s="45">
         <f t="shared" si="12"/>
         <v>2.6461980586249849</v>
       </c>
-      <c r="J35" s="25"/>
+      <c r="J35" s="24"/>
     </row>
     <row r="36" spans="2:11" ht="15.6">
       <c r="B36" s="15"/>
     </row>
     <row r="37" spans="2:11" ht="15.6">
-      <c r="B37" s="72" t="s">
+      <c r="B37" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="23"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="2:11" ht="15.75" customHeight="1">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="23"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="39" spans="2:11" ht="15.6">
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="66"/>
-      <c r="E39" s="67"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="65" t="s">
+      <c r="G39" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="66"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="24"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="23"/>
     </row>
     <row r="40" spans="2:11" ht="15.6">
-      <c r="B40" s="78"/>
-      <c r="C40" s="80" t="s">
+      <c r="B40" s="56"/>
+      <c r="C40" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="57" t="s">
+      <c r="D40" s="61"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="80" t="s">
+      <c r="G40" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="81"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="24"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="2:11" ht="31.2">
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="56" t="s">
+      <c r="C41" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="56" t="s">
+      <c r="D41" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="56" t="s">
+      <c r="E41" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="56" t="s">
+      <c r="F41" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="53" t="s">
+      <c r="G41" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="53" t="s">
+      <c r="H41" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="53" t="s">
+      <c r="I41" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="24"/>
+      <c r="J41" s="23"/>
     </row>
     <row r="42" spans="2:11" ht="15.6">
-      <c r="B42" s="21">
+      <c r="B42" s="17">
         <v>-35</v>
       </c>
-      <c r="C42" s="50">
+      <c r="C42" s="42">
         <v>57.008568351053704</v>
       </c>
       <c r="D42" s="19">
@@ -25510,28 +25499,28 @@
         <f>C42*0.86</f>
         <v>49.027368781906183</v>
       </c>
-      <c r="F42" s="50">
+      <c r="F42" s="42">
         <v>24.15014386971626</v>
       </c>
-      <c r="G42" s="54">
+      <c r="G42" s="45">
         <f t="shared" ref="G42:G47" si="15">C42/F42</f>
         <v>2.3605891815220685</v>
       </c>
-      <c r="H42" s="54">
+      <c r="H42" s="45">
         <f t="shared" ref="H42:H47" si="16">D42/F42</f>
         <v>8.0496091089902535</v>
       </c>
-      <c r="I42" s="54">
+      <c r="I42" s="45">
         <f t="shared" ref="I42:I47" si="17">E42/F42</f>
         <v>2.0301066961089789</v>
       </c>
-      <c r="J42" s="25"/>
+      <c r="J42" s="24"/>
     </row>
     <row r="43" spans="2:11" ht="15.6">
-      <c r="B43" s="21">
+      <c r="B43" s="17">
         <v>-30</v>
       </c>
-      <c r="C43" s="50">
+      <c r="C43" s="42">
         <v>67.926059975214514</v>
       </c>
       <c r="D43" s="19">
@@ -25542,28 +25531,28 @@
         <f t="shared" ref="E43:E47" si="19">C43*0.86</f>
         <v>58.416411578684482</v>
       </c>
-      <c r="F43" s="50">
+      <c r="F43" s="42">
         <v>27.771515391618845</v>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="45">
         <f t="shared" si="15"/>
         <v>2.4458895748884446</v>
       </c>
-      <c r="H43" s="54">
+      <c r="H43" s="45">
         <f t="shared" si="16"/>
         <v>8.3404834503695966</v>
       </c>
-      <c r="I43" s="54">
+      <c r="I43" s="45">
         <f t="shared" si="17"/>
         <v>2.1034650344040622</v>
       </c>
-      <c r="J43" s="25"/>
+      <c r="J43" s="24"/>
     </row>
     <row r="44" spans="2:11" ht="15.6">
-      <c r="B44" s="21">
+      <c r="B44" s="17">
         <v>-25</v>
       </c>
-      <c r="C44" s="50">
+      <c r="C44" s="42">
         <v>81.264036107502619</v>
       </c>
       <c r="D44" s="19">
@@ -25574,28 +25563,28 @@
         <f t="shared" si="19"/>
         <v>69.887071052452256</v>
       </c>
-      <c r="F44" s="50">
+      <c r="F44" s="42">
         <v>31.326351040161114</v>
       </c>
-      <c r="G44" s="54">
+      <c r="G44" s="45">
         <f t="shared" si="15"/>
         <v>2.5941111367653455</v>
       </c>
-      <c r="H44" s="54">
+      <c r="H44" s="45">
         <f t="shared" si="16"/>
         <v>8.8459189763698287</v>
       </c>
-      <c r="I44" s="54">
+      <c r="I44" s="45">
         <f t="shared" si="17"/>
         <v>2.2309355776181974</v>
       </c>
-      <c r="J44" s="25"/>
+      <c r="J44" s="24"/>
     </row>
     <row r="45" spans="2:11" ht="15.6">
-      <c r="B45" s="21">
+      <c r="B45" s="17">
         <v>-20</v>
       </c>
-      <c r="C45" s="50">
+      <c r="C45" s="42">
         <v>97.42064235331307</v>
       </c>
       <c r="D45" s="19">
@@ -25606,28 +25595,28 @@
         <f t="shared" si="19"/>
         <v>83.781752423849241</v>
       </c>
-      <c r="F45" s="50">
+      <c r="F45" s="42">
         <v>34.684632220816979</v>
       </c>
-      <c r="G45" s="54">
+      <c r="G45" s="45">
         <f t="shared" si="15"/>
         <v>2.8087552358373653</v>
       </c>
-      <c r="H45" s="54">
+      <c r="H45" s="45">
         <f t="shared" si="16"/>
         <v>9.5778553542054148</v>
       </c>
-      <c r="I45" s="54">
+      <c r="I45" s="45">
         <f t="shared" si="17"/>
         <v>2.4155295028201342</v>
       </c>
-      <c r="J45" s="25"/>
+      <c r="J45" s="24"/>
     </row>
     <row r="46" spans="2:11" ht="15.6">
-      <c r="B46" s="21">
+      <c r="B46" s="17">
         <v>-15</v>
       </c>
-      <c r="C46" s="50">
+      <c r="C46" s="42">
         <v>116.79402431804093</v>
       </c>
       <c r="D46" s="19">
@@ -25638,28 +25627,28 @@
         <f t="shared" si="19"/>
         <v>100.44286091351519</v>
       </c>
-      <c r="F46" s="50">
+      <c r="F46" s="42">
         <v>37.71634033906038</v>
       </c>
-      <c r="G46" s="54">
+      <c r="G46" s="45">
         <f t="shared" si="15"/>
         <v>3.0966425498362811</v>
       </c>
-      <c r="H46" s="54">
+      <c r="H46" s="45">
         <f t="shared" si="16"/>
         <v>10.559551094941719</v>
       </c>
-      <c r="I46" s="54">
+      <c r="I46" s="45">
         <f t="shared" si="17"/>
         <v>2.6631125928592017</v>
       </c>
-      <c r="J46" s="25"/>
+      <c r="J46" s="24"/>
     </row>
     <row r="47" spans="2:11" ht="15.6">
-      <c r="B47" s="21">
+      <c r="B47" s="17">
         <v>-10</v>
       </c>
-      <c r="C47" s="50">
+      <c r="C47" s="42">
         <v>139.78232760708116</v>
       </c>
       <c r="D47" s="19">
@@ -25670,90 +25659,90 @@
         <f t="shared" si="19"/>
         <v>120.21280174208979</v>
       </c>
-      <c r="F47" s="50">
+      <c r="F47" s="42">
         <v>40.291456800365268</v>
       </c>
-      <c r="G47" s="54">
+      <c r="G47" s="45">
         <f t="shared" si="15"/>
         <v>3.4692795621580488</v>
       </c>
-      <c r="H47" s="54">
+      <c r="H47" s="45">
         <f t="shared" si="16"/>
         <v>11.830243306958947</v>
       </c>
-      <c r="I47" s="54">
+      <c r="I47" s="45">
         <f t="shared" si="17"/>
         <v>2.9835804234559222</v>
       </c>
-      <c r="J47" s="25"/>
+      <c r="J47" s="24"/>
     </row>
     <row r="48" spans="2:11" ht="15.6">
       <c r="B48" s="15"/>
     </row>
     <row r="49" spans="2:11" ht="15.6">
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="23"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="88"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="88"/>
+      <c r="H49" s="88"/>
+      <c r="I49" s="89"/>
+      <c r="J49" s="22"/>
     </row>
     <row r="50" spans="2:11" ht="15.75" customHeight="1">
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="69"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="23"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="22"/>
     </row>
     <row r="51" spans="2:11" ht="15.6">
-      <c r="B51" s="77" t="s">
+      <c r="B51" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="C51" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="66"/>
-      <c r="E51" s="67"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="59"/>
       <c r="F51" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G51" s="65" t="s">
+      <c r="G51" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H51" s="66"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="24"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="23"/>
     </row>
     <row r="52" spans="2:11" ht="15.6">
-      <c r="B52" s="78"/>
-      <c r="C52" s="80" t="s">
+      <c r="B52" s="56"/>
+      <c r="C52" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="57" t="s">
+      <c r="D52" s="61"/>
+      <c r="E52" s="62"/>
+      <c r="F52" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="80" t="s">
+      <c r="G52" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H52" s="81"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="24"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="62"/>
+      <c r="J52" s="23"/>
     </row>
     <row r="53" spans="2:11" ht="31.2">
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C53" s="14" t="s">
@@ -25768,54 +25757,54 @@
       <c r="F53" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="21" t="s">
+      <c r="G53" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I53" s="21" t="s">
+      <c r="I53" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J53" s="24"/>
+      <c r="J53" s="23"/>
     </row>
     <row r="54" spans="2:11" ht="15.6">
       <c r="B54" s="17">
         <v>-35</v>
       </c>
-      <c r="C54" s="50">
+      <c r="C54" s="85">
         <v>62.010327145854134</v>
       </c>
       <c r="D54" s="19">
         <f>C54*3.41</f>
         <v>211.45521556736261</v>
       </c>
-      <c r="E54" s="19">
+      <c r="E54" s="86">
         <f>C54*0.86</f>
         <v>53.328881345434553</v>
       </c>
-      <c r="F54" s="50">
+      <c r="F54" s="85">
         <v>22.974852287715816</v>
       </c>
-      <c r="G54" s="54">
+      <c r="G54" s="45">
         <f t="shared" ref="G54:G59" si="20">C54/F54</f>
         <v>2.6990522667695145</v>
       </c>
-      <c r="H54" s="54">
+      <c r="H54" s="45">
         <f t="shared" ref="H54:H59" si="21">D54/F54</f>
         <v>9.2037682296840444</v>
       </c>
-      <c r="I54" s="54">
+      <c r="I54" s="45">
         <f t="shared" ref="I54:I59" si="22">E54/F54</f>
         <v>2.3211849494217822</v>
       </c>
-      <c r="J54" s="25"/>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="2:11" ht="15.6">
       <c r="B55" s="17">
         <v>-30</v>
       </c>
-      <c r="C55" s="50">
+      <c r="C55" s="42">
         <v>72.928564194420403</v>
       </c>
       <c r="D55" s="19">
@@ -25826,61 +25815,61 @@
         <f t="shared" ref="E55:E59" si="24">C55*0.86</f>
         <v>62.718565207201543</v>
       </c>
-      <c r="F55" s="50">
+      <c r="F55" s="42">
         <v>26.232909844766304</v>
       </c>
-      <c r="G55" s="54">
+      <c r="G55" s="45">
         <f t="shared" si="20"/>
         <v>2.7800409724264838</v>
       </c>
-      <c r="H55" s="54">
+      <c r="H55" s="45">
         <f t="shared" si="21"/>
         <v>9.4799397159743108</v>
       </c>
-      <c r="I55" s="54">
+      <c r="I55" s="45">
         <f t="shared" si="22"/>
         <v>2.390835236286776</v>
       </c>
-      <c r="J55" s="25"/>
-      <c r="K55" s="27"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="26"/>
     </row>
     <row r="56" spans="2:11" ht="15.6">
       <c r="B56" s="17">
         <v>-25</v>
       </c>
-      <c r="C56" s="50">
+      <c r="C56" s="85">
         <v>86.267684992786315</v>
       </c>
       <c r="D56" s="19">
         <f t="shared" si="23"/>
         <v>294.17280582540133</v>
       </c>
-      <c r="E56" s="19">
+      <c r="E56" s="86">
         <f t="shared" si="24"/>
         <v>74.190209093796227</v>
       </c>
-      <c r="F56" s="50">
+      <c r="F56" s="85">
         <v>29.358355457071273</v>
       </c>
-      <c r="G56" s="54">
+      <c r="G56" s="45">
         <f t="shared" si="20"/>
         <v>2.9384372404281871</v>
       </c>
-      <c r="H56" s="54">
+      <c r="H56" s="45">
         <f t="shared" si="21"/>
         <v>10.020070989860118</v>
       </c>
-      <c r="I56" s="54">
+      <c r="I56" s="45">
         <f t="shared" si="22"/>
         <v>2.5270560267682405</v>
       </c>
-      <c r="J56" s="25"/>
+      <c r="J56" s="24"/>
     </row>
     <row r="57" spans="2:11" ht="15.6">
       <c r="B57" s="17">
         <v>-20</v>
       </c>
-      <c r="C57" s="50">
+      <c r="C57" s="42">
         <v>102.42583514634686</v>
       </c>
       <c r="D57" s="19">
@@ -25891,60 +25880,60 @@
         <f t="shared" si="24"/>
         <v>88.086218225858289</v>
       </c>
-      <c r="F57" s="50">
+      <c r="F57" s="42">
         <v>32.221170530104573</v>
       </c>
-      <c r="G57" s="54">
+      <c r="G57" s="45">
         <f t="shared" si="20"/>
         <v>3.1788365680461341</v>
       </c>
-      <c r="H57" s="54">
+      <c r="H57" s="45">
         <f t="shared" si="21"/>
         <v>10.839832697037318</v>
       </c>
-      <c r="I57" s="54">
+      <c r="I57" s="45">
         <f t="shared" si="22"/>
         <v>2.733799448519675</v>
       </c>
-      <c r="J57" s="25"/>
+      <c r="J57" s="24"/>
     </row>
     <row r="58" spans="2:11" ht="15.6">
       <c r="B58" s="17">
         <v>-15</v>
       </c>
-      <c r="C58" s="50">
+      <c r="C58" s="85">
         <v>121.80116026049711</v>
       </c>
       <c r="D58" s="19">
         <f t="shared" si="23"/>
         <v>415.34195648829518</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="86">
         <f t="shared" si="24"/>
         <v>104.74899782402751</v>
       </c>
-      <c r="F58" s="50">
+      <c r="F58" s="85">
         <v>34.6913364693402</v>
       </c>
-      <c r="G58" s="54">
+      <c r="G58" s="45">
         <f t="shared" si="20"/>
         <v>3.5109964808690366</v>
       </c>
-      <c r="H58" s="54">
+      <c r="H58" s="45">
         <f t="shared" si="21"/>
         <v>11.972497999763416</v>
       </c>
-      <c r="I58" s="54">
+      <c r="I58" s="45">
         <f t="shared" si="22"/>
         <v>3.0194569735473715</v>
       </c>
-      <c r="J58" s="25"/>
+      <c r="J58" s="24"/>
     </row>
     <row r="59" spans="2:11" ht="15.6">
       <c r="B59" s="17">
         <v>-10</v>
       </c>
-      <c r="C59" s="50">
+      <c r="C59" s="42">
         <v>144.79180594063209</v>
       </c>
       <c r="D59" s="19">
@@ -25955,112 +25944,112 @@
         <f t="shared" si="24"/>
         <v>124.52095310894359</v>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="42">
         <v>36.638834680252081</v>
       </c>
-      <c r="G59" s="54">
+      <c r="G59" s="45">
         <f t="shared" si="20"/>
         <v>3.9518671159777155</v>
       </c>
-      <c r="H59" s="54">
+      <c r="H59" s="45">
         <f t="shared" si="21"/>
         <v>13.47586686548401</v>
       </c>
-      <c r="I59" s="54">
+      <c r="I59" s="45">
         <f t="shared" si="22"/>
         <v>3.3986057197408348</v>
       </c>
-      <c r="J59" s="25"/>
+      <c r="J59" s="24"/>
     </row>
     <row r="62" spans="2:11" ht="15.6">
-      <c r="B62" s="72" t="s">
+      <c r="B62" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
     </row>
     <row r="63" spans="2:11" ht="15.75" customHeight="1">
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="71"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="54"/>
     </row>
     <row r="64" spans="2:11" ht="15.6">
-      <c r="B64" s="77" t="s">
+      <c r="B64" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="65" t="s">
+      <c r="C64" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="66"/>
-      <c r="E64" s="67"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="59"/>
       <c r="F64" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="65" t="s">
+      <c r="G64" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="H64" s="66"/>
-      <c r="I64" s="67"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="59"/>
     </row>
     <row r="65" spans="2:10" ht="15.6">
-      <c r="B65" s="78"/>
-      <c r="C65" s="80" t="s">
+      <c r="B65" s="56"/>
+      <c r="C65" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D65" s="81"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="57" t="s">
+      <c r="D65" s="61"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G65" s="80" t="s">
+      <c r="G65" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="H65" s="81"/>
-      <c r="I65" s="82"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="62"/>
     </row>
     <row r="66" spans="2:10" ht="31.2">
-      <c r="B66" s="53" t="s">
+      <c r="B66" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="56" t="s">
+      <c r="D66" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="56" t="s">
+      <c r="E66" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F66" s="56" t="s">
+      <c r="F66" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="G66" s="53" t="s">
+      <c r="G66" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="53" t="s">
+      <c r="H66" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I66" s="53" t="s">
+      <c r="I66" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="15.6">
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C67" s="50">
+      <c r="C67" s="42">
         <v>72</v>
       </c>
       <c r="D67" s="19">
@@ -26071,18 +26060,18 @@
         <f>C67*0.86</f>
         <v>61.92</v>
       </c>
-      <c r="F67" s="50">
+      <c r="F67" s="42">
         <f>C67/G67</f>
         <v>38.095238095238095</v>
       </c>
-      <c r="G67" s="54">
+      <c r="G67" s="45">
         <v>1.89</v>
       </c>
-      <c r="H67" s="54">
+      <c r="H67" s="45">
         <f>G67*3.412</f>
         <v>6.4486799999999995</v>
       </c>
-      <c r="I67" s="54">
+      <c r="I67" s="45">
         <f>G67*0.86</f>
         <v>1.6254</v>
       </c>
@@ -26094,6 +26083,41 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="G52:I52"/>
     <mergeCell ref="B62:I62"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="B64:B65"/>
@@ -26101,41 +26125,6 @@
     <mergeCell ref="G64:I64"/>
     <mergeCell ref="C65:E65"/>
     <mergeCell ref="G65:I65"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
